--- a/data/dimensions/dimensions.xlsx
+++ b/data/dimensions/dimensions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GIT\cross_back\initial_data\classifications\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9437E5C-718D-41CA-B2A9-2CCBCB9F117F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303C2C7F-FCCE-457C-8507-2B20BC5AA717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="1080" windowWidth="30900" windowHeight="14460" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="21" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2218" uniqueCount="1339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2218" uniqueCount="1338">
   <si>
     <t>id</t>
   </si>
@@ -3368,9 +3368,6 @@
   </si>
   <si>
     <t>variant</t>
-  </si>
-  <si>
-    <t>explanation</t>
   </si>
   <si>
     <t>abroad-together</t>
@@ -4478,176 +4475,176 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1272</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>1273</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>1274</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>1275</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>1277</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>1278</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>1280</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>1281</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>1283</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>1284</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>1285</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>1286</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>1288</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>1289</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>1291</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>1292</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>1294</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>1295</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>1297</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>1298</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>1300</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>1301</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>1303</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>1304</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>1305</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>1306</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
   </sheetData>
@@ -8292,148 +8289,148 @@
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>1307</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>1308</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>1309</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>1106</v>
       </c>
       <c r="F1" s="7" t="s">
+        <v>1309</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>1310</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>1311</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>1312</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>1313</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>1314</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>1315</v>
       </c>
       <c r="D2" s="7">
         <v>2020</v>
       </c>
       <c r="F2" s="7" t="s">
+        <v>1315</v>
+      </c>
+      <c r="G2" s="7" t="s">
         <v>1316</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="H2" s="5" t="s">
         <v>1317</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>1319</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>1320</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>1321</v>
       </c>
       <c r="D3" s="7">
         <v>2017</v>
       </c>
       <c r="E3" s="7" t="s">
+        <v>1321</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>1322</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="I3" s="2" t="s">
         <v>1323</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>1324</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="D4" s="7">
         <v>2024</v>
       </c>
       <c r="F4" s="7" t="s">
+        <v>1325</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>1326</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>1327</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="D5" s="7">
         <v>2024</v>
       </c>
       <c r="F5" s="7" t="s">
+        <v>1328</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>1329</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>1330</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>1331</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="D6" s="7">
         <v>2024</v>
       </c>
       <c r="F6" s="7" t="s">
+        <v>1331</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>1332</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>1333</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>1334</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="D7" s="7">
         <v>2025</v>
       </c>
       <c r="F7" s="9" t="s">
+        <v>1335</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>1336</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>1337</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>1338</v>
       </c>
     </row>
   </sheetData>
@@ -11988,1231 +11985,1231 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1109</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>1110</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>1111</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>1112</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>1110</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>1113</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>1114</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>1114</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>1115</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>1116</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1116</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>1117</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>1118</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>1118</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>1119</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>1110</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>1111</v>
-      </c>
       <c r="C6" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>1120</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>1110</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>1121</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>1124</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>1120</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>1118</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>1125</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>1110</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>1111</v>
-      </c>
       <c r="C10" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>1126</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>1110</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>1131</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>1132</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>1133</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>1134</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>1135</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>1136</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>1138</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>1139</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>1141</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>1142</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>1144</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>1145</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>1147</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>1148</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>1150</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>1151</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>1152</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>1153</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>1154</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>1155</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>1131</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>1132</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>1120</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>1133</v>
-      </c>
       <c r="E22" s="2" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>1135</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1120</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>1136</v>
-      </c>
       <c r="E23" s="2" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>1138</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>1120</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>1139</v>
-      </c>
       <c r="E24" s="2" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>1141</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1120</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>1142</v>
-      </c>
       <c r="E25" s="2" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>1144</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>1120</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>1145</v>
-      </c>
       <c r="E26" s="2" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>1147</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>1120</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>1148</v>
-      </c>
       <c r="E27" s="2" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>1150</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>1120</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>1151</v>
-      </c>
       <c r="E28" s="2" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>1153</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>1120</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>1154</v>
-      </c>
       <c r="E29" s="2" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>1131</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="C30" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>1132</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>1126</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>1133</v>
-      </c>
       <c r="E30" s="2" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>1135</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>1126</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>1136</v>
-      </c>
       <c r="E31" s="2" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>1138</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>1126</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>1139</v>
-      </c>
       <c r="E32" s="2" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>1141</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>1126</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>1142</v>
-      </c>
       <c r="E33" s="2" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>1144</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>1126</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>1145</v>
-      </c>
       <c r="E34" s="2" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>1147</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>1126</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>1148</v>
-      </c>
       <c r="E35" s="2" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>1150</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>1126</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>1151</v>
-      </c>
       <c r="E36" s="2" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>1153</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>1126</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>1154</v>
-      </c>
       <c r="E37" s="2" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>1172</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="C38" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>1173</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>1175</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>1175</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>1176</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>1177</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>1177</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>1178</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>1179</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>1179</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>1181</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>1181</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>1182</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>1183</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>1183</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>1184</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>1185</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>1185</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>1186</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>1187</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>1187</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>1188</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>1189</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>1189</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>1190</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>1191</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>1191</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>1193</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>1193</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>1194</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>1195</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>1195</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>1196</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>1172</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>1173</v>
-      </c>
       <c r="C50" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>1197</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>1172</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>1173</v>
-      </c>
       <c r="C62" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>1210</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
     </row>
   </sheetData>
@@ -13233,7 +13230,7 @@
         <v>1106</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>3</v>
@@ -13244,223 +13241,223 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>1224</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>1225</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>1226</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>1225</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>1227</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>1228</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>1229</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>1230</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>1229</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>1231</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>1232</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>1233</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>1234</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1233</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>1236</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>1237</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>1238</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>1237</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>1240</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>1241</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>1242</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>1241</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>1244</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>1245</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>1246</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>1246</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>1247</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>1248</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>1249</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>1250</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>1249</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>1251</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>1252</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>1253</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>1252</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>1254</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>1253</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>1256</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>1257</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>1258</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>1257</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>1260</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>1261</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>1262</v>
-      </c>
       <c r="D11" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>1261</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>1262</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>1263</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>1264</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>1265</v>
-      </c>
       <c r="D12" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>1264</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>1265</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>1266</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>1267</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>1267</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>1267</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>1268</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>1269</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>1270</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>1270</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>1270</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>1271</v>
       </c>
     </row>
   </sheetData>

--- a/data/dimensions/dimensions.xlsx
+++ b/data/dimensions/dimensions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GIT\cross_back\initial_data\classifications\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GIT\data_model_tmp\data\dimensions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303C2C7F-FCCE-457C-8507-2B20BC5AA717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95217219-585C-4CF8-82DF-F6BE1421E25D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1080" windowWidth="30900" windowHeight="14460" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="1080" windowWidth="30900" windowHeight="14460" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="21" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2218" uniqueCount="1338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2220" uniqueCount="1340">
   <si>
     <t>id</t>
   </si>
@@ -4055,6 +4055,12 @@
   </si>
   <si>
     <t>https://www.bfe.admin.ch/ogd62</t>
+  </si>
+  <si>
+    <t>asd</t>
+  </si>
+  <si>
+    <t>other2</t>
   </si>
 </sst>
 </file>
@@ -12047,7 +12053,7 @@
         <v>1110</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1111</v>
+        <v>1338</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>1117</v>
@@ -13549,7 +13555,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -14159,6 +14165,17 @@
         <v>0</v>
       </c>
       <c r="D44" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="D45" t="s">
         <v>510</v>
       </c>
     </row>

--- a/data/dimensions/dimensions.xlsx
+++ b/data/dimensions/dimensions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GIT\data_model_tmp\data\dimensions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95217219-585C-4CF8-82DF-F6BE1421E25D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0B6235-AAAC-4EC3-A278-E3028FAB5FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1080" windowWidth="30900" windowHeight="14460" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="1080" windowWidth="30900" windowHeight="14460" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="21" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2220" uniqueCount="1340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2221" uniqueCount="1339">
   <si>
     <t>id</t>
   </si>
@@ -1910,9 +1910,6 @@
   </si>
   <si>
     <t>residential</t>
-  </si>
-  <si>
-    <t>Residential</t>
   </si>
   <si>
     <t>transport</t>
@@ -4481,176 +4478,176 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1271</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>1272</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>1273</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>1274</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>1275</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>1276</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>1277</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>1279</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>1280</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>1282</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>1283</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>1284</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>1285</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>1287</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>1288</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>1290</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>1291</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>1293</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>1294</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>1296</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>1297</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>1299</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>1300</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>1302</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>1303</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>1304</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>1305</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
   </sheetData>
@@ -4699,12 +4696,12 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -4713,15 +4710,15 @@
         <v>618</v>
       </c>
       <c r="D3" t="s">
+        <v>627</v>
+      </c>
+      <c r="E3" t="s">
         <v>628</v>
-      </c>
-      <c r="E3" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -4730,12 +4727,12 @@
         <v>618</v>
       </c>
       <c r="D4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -4744,12 +4741,12 @@
         <v>618</v>
       </c>
       <c r="D5" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -4758,12 +4755,12 @@
         <v>618</v>
       </c>
       <c r="D6" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -4772,12 +4769,12 @@
         <v>618</v>
       </c>
       <c r="D7" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -4786,12 +4783,12 @@
         <v>618</v>
       </c>
       <c r="D8" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -4800,7 +4797,7 @@
         <v>618</v>
       </c>
       <c r="D9" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -4811,7 +4808,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -4822,12 +4819,12 @@
         <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -4836,12 +4833,12 @@
         <v>622</v>
       </c>
       <c r="D12" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -4850,12 +4847,12 @@
         <v>622</v>
       </c>
       <c r="D13" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -4864,7 +4861,7 @@
         <v>622</v>
       </c>
       <c r="D14" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -4907,245 +4904,245 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>649</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
         <v>650</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>651</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
         <v>652</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="D3" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>653</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
         <v>654</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="D4" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>655</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>653</v>
+      </c>
+      <c r="D5" t="s">
         <v>656</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
-        <v>654</v>
-      </c>
-      <c r="D5" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D6" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D8" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D9" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>665</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>653</v>
+      </c>
+      <c r="D10" t="s">
         <v>666</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
-        <v>654</v>
-      </c>
-      <c r="D10" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D11" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D13" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D14" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>675</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>653</v>
+      </c>
+      <c r="D15" t="s">
         <v>676</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" t="s">
-        <v>654</v>
-      </c>
-      <c r="D15" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D16" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D17" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D18" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>683</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>653</v>
+      </c>
+      <c r="D19" t="s">
         <v>684</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
-        <v>654</v>
-      </c>
-      <c r="D19" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -5188,66 +5185,66 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>685</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
         <v>686</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>687</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
         <v>688</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="D3" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>689</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>687</v>
+      </c>
+      <c r="D4" t="s">
         <v>690</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>688</v>
-      </c>
-      <c r="D4" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>691</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>687</v>
+      </c>
+      <c r="D5" t="s">
         <v>692</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
-        <v>688</v>
-      </c>
-      <c r="D5" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>693</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>687</v>
+      </c>
+      <c r="D6" t="s">
         <v>694</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>688</v>
-      </c>
-      <c r="D6" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -5294,77 +5291,77 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>695</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
         <v>696</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>697</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
         <v>698</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="D3" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>699</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>697</v>
+      </c>
+      <c r="D4" t="s">
         <v>700</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>698</v>
-      </c>
-      <c r="D4" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>701</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>697</v>
+      </c>
+      <c r="D5" t="s">
         <v>702</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
-        <v>698</v>
-      </c>
-      <c r="D5" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>703</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>697</v>
+      </c>
+      <c r="D6" t="s">
         <v>704</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>698</v>
-      </c>
-      <c r="D6" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>705</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
         <v>706</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="D7" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -5380,7 +5377,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -5403,12 +5400,12 @@
         <v>523</v>
       </c>
       <c r="D10" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -5417,12 +5414,12 @@
         <v>554</v>
       </c>
       <c r="D11" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -5431,7 +5428,7 @@
         <v>554</v>
       </c>
       <c r="D12" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -5532,7 +5529,7 @@
         <v>562</v>
       </c>
       <c r="D19" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -5546,7 +5543,7 @@
         <v>567</v>
       </c>
       <c r="D20" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -5560,7 +5557,7 @@
         <v>567</v>
       </c>
       <c r="D21" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -5574,7 +5571,7 @@
         <v>567</v>
       </c>
       <c r="D22" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -5588,7 +5585,7 @@
         <v>567</v>
       </c>
       <c r="D23" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -5621,710 +5618,710 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>718</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="D26" t="s">
         <v>719</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-      <c r="D26" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>720</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>718</v>
+      </c>
+      <c r="D27" t="s">
         <v>721</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27" t="s">
-        <v>719</v>
-      </c>
-      <c r="D27" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>722</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>718</v>
+      </c>
+      <c r="D28" t="s">
         <v>723</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28" t="s">
-        <v>719</v>
-      </c>
-      <c r="D28" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>724</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>718</v>
+      </c>
+      <c r="D29" t="s">
         <v>725</v>
-      </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-      <c r="C29" t="s">
-        <v>719</v>
-      </c>
-      <c r="D29" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>726</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="D30" t="s">
         <v>727</v>
-      </c>
-      <c r="B30">
-        <v>0</v>
-      </c>
-      <c r="D30" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>728</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>726</v>
+      </c>
+      <c r="D31" t="s">
         <v>729</v>
-      </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
-        <v>727</v>
-      </c>
-      <c r="D31" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B32">
         <v>2</v>
       </c>
       <c r="C32" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D32" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B33">
         <v>3</v>
       </c>
       <c r="C33" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D33" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B34">
         <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D34" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B35">
         <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D35" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B36">
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D36" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B37">
         <v>3</v>
       </c>
       <c r="C37" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D37" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B38">
         <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D38" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B39">
         <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D39" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B40">
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D40" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B41">
         <v>3</v>
       </c>
       <c r="C41" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D41" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B42">
         <v>3</v>
       </c>
       <c r="C42" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D42" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B43">
         <v>3</v>
       </c>
       <c r="C43" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D43" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B44">
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D44" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>756</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45" t="s">
+        <v>726</v>
+      </c>
+      <c r="D45" t="s">
         <v>757</v>
-      </c>
-      <c r="B45">
-        <v>1</v>
-      </c>
-      <c r="C45" t="s">
-        <v>727</v>
-      </c>
-      <c r="D45" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B46">
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D46" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B47">
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D47" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B48">
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D48" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>764</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
+        <v>726</v>
+      </c>
+      <c r="D49" t="s">
         <v>765</v>
-      </c>
-      <c r="B49">
-        <v>1</v>
-      </c>
-      <c r="C49" t="s">
-        <v>727</v>
-      </c>
-      <c r="D49" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B50">
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D50" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B51">
         <v>3</v>
       </c>
       <c r="C51" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D51" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B52">
         <v>3</v>
       </c>
       <c r="C52" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D52" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B53">
         <v>3</v>
       </c>
       <c r="C53" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D53" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B54">
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D54" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B55">
         <v>3</v>
       </c>
       <c r="C55" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D55" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B56">
         <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D56" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B57">
         <v>3</v>
       </c>
       <c r="C57" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D57" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B58">
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D58" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B59">
         <v>3</v>
       </c>
       <c r="C59" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D59" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B60">
         <v>3</v>
       </c>
       <c r="C60" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D60" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B61">
         <v>3</v>
       </c>
       <c r="C61" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D61" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B62">
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D62" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
+        <v>792</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="C63" t="s">
+        <v>726</v>
+      </c>
+      <c r="D63" t="s">
         <v>793</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
-      </c>
-      <c r="C63" t="s">
-        <v>727</v>
-      </c>
-      <c r="D63" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B64">
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D64" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B65">
         <v>3</v>
       </c>
       <c r="C65" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D65" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B66">
         <v>3</v>
       </c>
       <c r="C66" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D66" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B67">
         <v>3</v>
       </c>
       <c r="C67" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D67" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B68">
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D68" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B69">
         <v>3</v>
       </c>
       <c r="C69" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="D69" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B70">
         <v>3</v>
       </c>
       <c r="C70" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="D70" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B71">
         <v>3</v>
       </c>
       <c r="C71" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="D71" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B72">
         <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D72" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B73">
         <v>3</v>
       </c>
       <c r="C73" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D73" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B74">
         <v>3</v>
       </c>
       <c r="C74" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D74" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B75">
         <v>3</v>
       </c>
       <c r="C75" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D75" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B76">
         <v>2</v>
       </c>
       <c r="C76" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D76" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -6335,315 +6332,315 @@
         <v>1</v>
       </c>
       <c r="C77" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D77" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>821</v>
+      </c>
+      <c r="B78">
+        <v>1</v>
+      </c>
+      <c r="C78" t="s">
+        <v>726</v>
+      </c>
+      <c r="D78" t="s">
         <v>822</v>
-      </c>
-      <c r="B78">
-        <v>1</v>
-      </c>
-      <c r="C78" t="s">
-        <v>727</v>
-      </c>
-      <c r="D78" t="s">
-        <v>823</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B79">
         <v>2</v>
       </c>
       <c r="C79" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D79" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B80">
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D80" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B81">
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D81" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B82">
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D82" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B83">
         <v>2</v>
       </c>
       <c r="C83" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D83" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B84">
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D84" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B85">
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D85" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B86">
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D86" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B87">
         <v>2</v>
       </c>
       <c r="C87" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D87" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
+        <v>841</v>
+      </c>
+      <c r="B88">
+        <v>1</v>
+      </c>
+      <c r="C88" t="s">
+        <v>726</v>
+      </c>
+      <c r="D88" t="s">
         <v>842</v>
-      </c>
-      <c r="B88">
-        <v>1</v>
-      </c>
-      <c r="C88" t="s">
-        <v>727</v>
-      </c>
-      <c r="D88" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B89">
         <v>2</v>
       </c>
       <c r="C89" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="D89" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B90">
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="D90" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B91">
         <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="D91" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B92">
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="D92" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B93">
         <v>2</v>
       </c>
       <c r="C93" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="D93" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B94">
         <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D94" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B95">
         <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D95" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B96">
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D96" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B97">
         <v>2</v>
       </c>
       <c r="C97" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="D97" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
+        <v>861</v>
+      </c>
+      <c r="B98">
+        <v>1</v>
+      </c>
+      <c r="C98" t="s">
+        <v>726</v>
+      </c>
+      <c r="D98" t="s">
         <v>862</v>
-      </c>
-      <c r="B98">
-        <v>1</v>
-      </c>
-      <c r="C98" t="s">
-        <v>727</v>
-      </c>
-      <c r="D98" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
+        <v>863</v>
+      </c>
+      <c r="B99">
+        <v>0</v>
+      </c>
+      <c r="D99" t="s">
         <v>864</v>
-      </c>
-      <c r="B99">
-        <v>0</v>
-      </c>
-      <c r="D99" t="s">
-        <v>865</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
@@ -6686,303 +6683,303 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>865</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
         <v>866</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>867</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>865</v>
+      </c>
+      <c r="D3" t="s">
         <v>868</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>866</v>
-      </c>
-      <c r="D3" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>869</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>865</v>
+      </c>
+      <c r="D4" t="s">
         <v>870</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>866</v>
-      </c>
-      <c r="D4" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>871</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>865</v>
+      </c>
+      <c r="D5" t="s">
         <v>872</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
-        <v>866</v>
-      </c>
-      <c r="D5" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>873</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>865</v>
+      </c>
+      <c r="D6" t="s">
         <v>874</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>866</v>
-      </c>
-      <c r="D6" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>875</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>865</v>
+      </c>
+      <c r="D7" t="s">
         <v>876</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>866</v>
-      </c>
-      <c r="D7" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>877</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>865</v>
+      </c>
+      <c r="D8" t="s">
         <v>878</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
-        <v>866</v>
-      </c>
-      <c r="D8" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>879</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>865</v>
+      </c>
+      <c r="D9" t="s">
         <v>880</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
-        <v>866</v>
-      </c>
-      <c r="D9" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D10" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D11" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D12" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>887</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>865</v>
+      </c>
+      <c r="D13" t="s">
         <v>888</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
-        <v>866</v>
-      </c>
-      <c r="D13" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>889</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="D14" t="s">
         <v>890</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="D14" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="D15" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>892</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>889</v>
+      </c>
+      <c r="D16" t="s">
         <v>893</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" t="s">
-        <v>890</v>
-      </c>
-      <c r="D16" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="D17" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>895</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>889</v>
+      </c>
+      <c r="D18" t="s">
         <v>896</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18" t="s">
-        <v>890</v>
-      </c>
-      <c r="D18" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="D19" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="D20" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>899</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>889</v>
+      </c>
+      <c r="D21" t="s">
         <v>900</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
-        <v>890</v>
-      </c>
-      <c r="D21" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>901</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="D22" t="s">
         <v>902</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-      <c r="D22" t="s">
-        <v>903</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>903</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="D23" t="s">
         <v>904</v>
-      </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-      <c r="D23" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -6993,113 +6990,113 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>906</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="D25" t="s">
         <v>907</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="D25" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>908</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>906</v>
+      </c>
+      <c r="D26" t="s">
         <v>909</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26" t="s">
-        <v>907</v>
-      </c>
-      <c r="D26" t="s">
-        <v>910</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>910</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>906</v>
+      </c>
+      <c r="D27" t="s">
         <v>911</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27" t="s">
-        <v>907</v>
-      </c>
-      <c r="D27" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>912</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>906</v>
+      </c>
+      <c r="D28" t="s">
         <v>913</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28" t="s">
-        <v>907</v>
-      </c>
-      <c r="D28" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>914</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>906</v>
+      </c>
+      <c r="D29" t="s">
         <v>915</v>
-      </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-      <c r="C29" t="s">
-        <v>907</v>
-      </c>
-      <c r="D29" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>916</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="D30" t="s">
         <v>917</v>
-      </c>
-      <c r="B30">
-        <v>0</v>
-      </c>
-      <c r="D30" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>918</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="D31" t="s">
         <v>919</v>
-      </c>
-      <c r="B31">
-        <v>0</v>
-      </c>
-      <c r="D31" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>920</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="D32" t="s">
         <v>921</v>
-      </c>
-      <c r="B32">
-        <v>0</v>
-      </c>
-      <c r="D32" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>922</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="D33" t="s">
         <v>923</v>
-      </c>
-      <c r="B33">
-        <v>0</v>
-      </c>
-      <c r="D33" t="s">
-        <v>924</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -7148,12 +7145,12 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -7162,12 +7159,12 @@
         <v>601</v>
       </c>
       <c r="D3" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -7176,12 +7173,12 @@
         <v>601</v>
       </c>
       <c r="D4" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -7190,7 +7187,7 @@
         <v>601</v>
       </c>
       <c r="D5" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -7201,12 +7198,12 @@
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -7215,12 +7212,12 @@
         <v>609</v>
       </c>
       <c r="D7" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -7229,12 +7226,12 @@
         <v>609</v>
       </c>
       <c r="D8" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -7243,18 +7240,18 @@
         <v>609</v>
       </c>
       <c r="D9" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>937</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
         <v>938</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="D10" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -7265,60 +7262,60 @@
         <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>941</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>726</v>
+      </c>
+      <c r="D13" t="s">
         <v>942</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
-        <v>727</v>
-      </c>
-      <c r="D13" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>943</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>726</v>
+      </c>
+      <c r="D14" t="s">
         <v>944</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14" t="s">
-        <v>727</v>
-      </c>
-      <c r="D14" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>861</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>726</v>
+      </c>
+      <c r="D15" t="s">
         <v>862</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" t="s">
-        <v>727</v>
-      </c>
-      <c r="D15" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -7329,7 +7326,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -7372,99 +7369,99 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>946</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
         <v>947</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>948</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
         <v>949</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="D3" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>950</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>948</v>
+      </c>
+      <c r="D4" t="s">
         <v>951</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>949</v>
-      </c>
-      <c r="D4" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>952</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>948</v>
+      </c>
+      <c r="D5" t="s">
         <v>953</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
-        <v>949</v>
-      </c>
-      <c r="D5" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>954</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>948</v>
+      </c>
+      <c r="D6" t="s">
         <v>955</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>949</v>
-      </c>
-      <c r="D6" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>957</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
         <v>958</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="D8" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>959</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
         <v>960</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="D9" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -7507,102 +7504,102 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>961</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
         <v>962</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>963</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
         <v>964</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="D3" t="s">
-        <v>965</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>965</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>963</v>
+      </c>
+      <c r="D4" t="s">
         <v>966</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>964</v>
-      </c>
-      <c r="D4" t="s">
-        <v>967</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>967</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>963</v>
+      </c>
+      <c r="D5" t="s">
         <v>968</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
-        <v>964</v>
-      </c>
-      <c r="D5" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>969</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>963</v>
+      </c>
+      <c r="D6" t="s">
         <v>970</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>964</v>
-      </c>
-      <c r="D6" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>971</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
         <v>972</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="D7" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>973</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
         <v>974</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="D8" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>975</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
         <v>976</v>
       </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>977</v>
-      </c>
-      <c r="E9" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -7645,91 +7642,91 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>978</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
         <v>979</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>980</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
         <v>981</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="D3" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>982</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
         <v>983</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="D4" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>984</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>982</v>
+      </c>
+      <c r="D5" t="s">
         <v>985</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
-        <v>983</v>
-      </c>
-      <c r="D5" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>986</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>982</v>
+      </c>
+      <c r="D6" t="s">
         <v>987</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>983</v>
-      </c>
-      <c r="D6" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>988</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>982</v>
+      </c>
+      <c r="D7" t="s">
         <v>989</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>983</v>
-      </c>
-      <c r="D7" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>990</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
         <v>991</v>
       </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="D8" t="s">
-        <v>992</v>
-      </c>
       <c r="E8" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -7772,489 +7769,489 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>992</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
         <v>993</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>995</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
         <v>996</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="D4" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>997</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
         <v>998</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="D5" t="s">
-        <v>999</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D7" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D8" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>693</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>687</v>
+      </c>
+      <c r="D9" t="s">
         <v>694</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
-        <v>688</v>
-      </c>
-      <c r="D9" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
         <v>1003</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="D10" t="s">
-        <v>1004</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D11" t="s">
         <v>1005</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1003</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D12" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D13" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D14" t="s">
         <v>1009</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14" t="s">
-        <v>1003</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="D15" t="s">
         <v>1011</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="D16" t="s">
         <v>1013</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="D17" t="s">
         <v>1015</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="D18" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="D19" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D20" t="s">
         <v>1019</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D20" t="s">
-        <v>1020</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="D21" t="s">
         <v>1021</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="D21" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="D22" t="s">
         <v>1023</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-      <c r="D22" t="s">
-        <v>1024</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D23" t="s">
         <v>1025</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23" t="s">
-        <v>1023</v>
-      </c>
-      <c r="D23" t="s">
-        <v>1026</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D24" t="s">
         <v>1027</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24" t="s">
-        <v>1023</v>
-      </c>
-      <c r="D24" t="s">
-        <v>1028</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D25" t="s">
         <v>1029</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25" t="s">
-        <v>1023</v>
-      </c>
-      <c r="D25" t="s">
-        <v>1030</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D26" t="s">
         <v>1031</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26" t="s">
-        <v>1023</v>
-      </c>
-      <c r="D26" t="s">
-        <v>1032</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="D27" t="s">
         <v>1033</v>
-      </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
-      <c r="D27" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>685</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D28" t="s">
         <v>686</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28" t="s">
-        <v>1033</v>
-      </c>
-      <c r="D28" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="D29" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D30" t="s">
         <v>1036</v>
-      </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-      <c r="C30" t="s">
-        <v>1033</v>
-      </c>
-      <c r="D30" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="D31" t="s">
         <v>1038</v>
-      </c>
-      <c r="B31">
-        <v>0</v>
-      </c>
-      <c r="D31" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D32" t="s">
         <v>1040</v>
-      </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s">
-        <v>1038</v>
-      </c>
-      <c r="D32" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D33" t="s">
         <v>1042</v>
-      </c>
-      <c r="B33">
-        <v>1</v>
-      </c>
-      <c r="C33" t="s">
-        <v>1038</v>
-      </c>
-      <c r="D33" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D34" t="s">
         <v>1044</v>
-      </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-      <c r="C34" t="s">
-        <v>1038</v>
-      </c>
-      <c r="D34" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D35" t="s">
         <v>1046</v>
-      </c>
-      <c r="B35">
-        <v>1</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1038</v>
-      </c>
-      <c r="D35" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D37" t="s">
         <v>1049</v>
-      </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="C37" t="s">
-        <v>1048</v>
-      </c>
-      <c r="D37" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D38" t="s">
         <v>1051</v>
-      </c>
-      <c r="B38">
-        <v>1</v>
-      </c>
-      <c r="C38" t="s">
-        <v>1048</v>
-      </c>
-      <c r="D38" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="D39" t="s">
         <v>1053</v>
-      </c>
-      <c r="B39">
-        <v>0</v>
-      </c>
-      <c r="D39" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -8295,148 +8292,148 @@
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>1306</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>1307</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>1308</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>1106</v>
-      </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>1309</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>1310</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>1311</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>1312</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>1313</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>1314</v>
       </c>
       <c r="D2" s="7">
         <v>2020</v>
       </c>
       <c r="F2" s="7" t="s">
+        <v>1314</v>
+      </c>
+      <c r="G2" s="7" t="s">
         <v>1315</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="H2" s="5" t="s">
         <v>1316</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>1317</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>1318</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>1319</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>1320</v>
       </c>
       <c r="D3" s="7">
         <v>2017</v>
       </c>
       <c r="E3" s="7" t="s">
+        <v>1320</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>1321</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="I3" s="2" t="s">
         <v>1322</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>1323</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="D4" s="7">
         <v>2024</v>
       </c>
       <c r="F4" s="7" t="s">
+        <v>1324</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>1325</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="D5" s="7">
         <v>2024</v>
       </c>
       <c r="F5" s="7" t="s">
+        <v>1327</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>1328</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>1329</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="D6" s="7">
         <v>2024</v>
       </c>
       <c r="F6" s="7" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>1331</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>1332</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>1333</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="D7" s="7">
         <v>2025</v>
       </c>
       <c r="F7" s="9" t="s">
+        <v>1334</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>1335</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>1336</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>1337</v>
       </c>
     </row>
   </sheetData>
@@ -8472,269 +8469,269 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
         <v>1055</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1056</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>699</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D3" t="s">
         <v>700</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D3" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>756</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D4" t="s">
         <v>757</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D4" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D5" t="s">
         <v>1057</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1058</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D8" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D9" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>693</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>687</v>
+      </c>
+      <c r="D10" t="s">
         <v>694</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
-        <v>688</v>
-      </c>
-      <c r="D10" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
         <v>1063</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
         <v>1065</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="D13" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D14" t="s">
         <v>1068</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D15" t="s">
         <v>1070</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D16" t="s">
         <v>1019</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1020</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="D18" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
       <c r="D19" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D20" t="s">
         <v>1074</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1048</v>
-      </c>
-      <c r="D20" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D21" t="s">
         <v>1076</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
-        <v>1048</v>
-      </c>
-      <c r="D21" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D22" t="s">
         <v>1051</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22" t="s">
-        <v>1048</v>
-      </c>
-      <c r="D22" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -8777,185 +8774,185 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D5" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D6" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>693</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>687</v>
+      </c>
+      <c r="D7" t="s">
         <v>694</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>688</v>
-      </c>
-      <c r="D7" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
         <v>1084</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="D11" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="D12" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D13" t="s">
         <v>1019</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1020</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="D14" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -8998,196 +8995,196 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
         <v>1091</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1092</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D6" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D7" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>693</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>687</v>
+      </c>
+      <c r="D8" t="s">
         <v>694</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
-        <v>688</v>
-      </c>
-      <c r="D8" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
         <v>1099</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="D10" t="s">
-        <v>1100</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="D12" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="D13" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D14" t="s">
         <v>1019</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1020</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -11979,13 +11976,13 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1106</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1107</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1108</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
@@ -11996,1226 +11993,1226 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>1110</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>1111</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>1109</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>1112</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>1113</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1110</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>1113</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>1114</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>1115</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>1110</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1115</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>1117</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1110</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>1338</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>1117</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>1110</v>
-      </c>
       <c r="C6" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>1119</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>1109</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>1123</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>1110</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>1119</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>1117</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>1110</v>
-      </c>
       <c r="C10" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>1125</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>1109</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>1130</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>1131</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>1132</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>1133</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>1134</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>1135</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>1137</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>1138</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>1140</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>1141</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>1143</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>1144</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>1146</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>1147</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>1148</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>1149</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>1150</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>1151</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>1152</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>1153</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>1154</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>1130</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>1131</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>1119</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>1132</v>
-      </c>
       <c r="E22" s="2" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>1134</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1119</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>1135</v>
-      </c>
       <c r="E23" s="2" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>1137</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>1119</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>1138</v>
-      </c>
       <c r="E24" s="2" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>1140</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1119</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>1141</v>
-      </c>
       <c r="E25" s="2" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>1143</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>1119</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>1144</v>
-      </c>
       <c r="E26" s="2" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>1146</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>1119</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>1147</v>
-      </c>
       <c r="E27" s="2" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>1149</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>1119</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>1150</v>
-      </c>
       <c r="E28" s="2" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>1152</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>1119</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>1153</v>
-      </c>
       <c r="E29" s="2" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>1130</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="C30" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>1131</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>1125</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>1132</v>
-      </c>
       <c r="E30" s="2" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>1134</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>1125</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>1135</v>
-      </c>
       <c r="E31" s="2" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>1137</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>1125</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>1138</v>
-      </c>
       <c r="E32" s="2" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>1140</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>1125</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>1141</v>
-      </c>
       <c r="E33" s="2" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>1143</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>1125</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>1144</v>
-      </c>
       <c r="E34" s="2" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>1146</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>1125</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>1147</v>
-      </c>
       <c r="E35" s="2" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>1149</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>1125</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>1150</v>
-      </c>
       <c r="E36" s="2" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>1152</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>1125</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>1153</v>
-      </c>
       <c r="E37" s="2" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>1171</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="C38" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>1172</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>1171</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>1174</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>1174</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>1175</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>1176</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>1176</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>1177</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>1178</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>1178</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>1179</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>1180</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>1180</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>1181</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>1182</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>1182</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>1184</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>1184</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>1186</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>1186</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>1187</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>1188</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>1188</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>1189</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>1190</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>1190</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>1191</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>1192</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>1192</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>1194</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>1194</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>1195</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>1171</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>1172</v>
-      </c>
       <c r="C50" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>1196</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>1171</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>1171</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>1172</v>
-      </c>
       <c r="C62" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>1209</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>1171</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
   </sheetData>
@@ -13233,10 +13230,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>3</v>
@@ -13247,223 +13244,223 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>1223</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>1224</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>1225</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>1224</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>1226</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>1227</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>1228</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>1229</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>1228</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>1231</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>1232</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>1233</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1232</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>1235</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>1236</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>1237</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>1236</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>1239</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>1240</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>1241</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>1240</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>1242</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>1243</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>1244</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>1245</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>1245</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>1246</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>1247</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>1248</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>1249</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>1248</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>1250</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>1252</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>1253</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>1252</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>1254</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>1255</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>1256</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>1257</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>1256</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>1259</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>1260</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>1261</v>
-      </c>
       <c r="D11" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>1260</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>1262</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>1263</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>1264</v>
-      </c>
       <c r="D12" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>1263</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>1264</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>1265</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>1266</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>1266</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>1266</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>1267</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>1268</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>1269</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>1269</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>1269</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>1270</v>
       </c>
     </row>
   </sheetData>
@@ -14170,7 +14167,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -14186,7 +14183,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -14691,7 +14688,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B38">
         <v>3</v>
@@ -14700,12 +14697,12 @@
         <v>567</v>
       </c>
       <c r="D38" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B39">
         <v>3</v>
@@ -14714,12 +14711,12 @@
         <v>567</v>
       </c>
       <c r="D39" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B40">
         <v>3</v>
@@ -14728,12 +14725,12 @@
         <v>567</v>
       </c>
       <c r="D40" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B41">
         <v>3</v>
@@ -14742,40 +14739,40 @@
         <v>567</v>
       </c>
       <c r="D41" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C42" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="D42" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>579</v>
+        <v>562</v>
       </c>
       <c r="D43" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B44">
         <v>3</v>
@@ -14784,12 +14781,12 @@
         <v>579</v>
       </c>
       <c r="D44" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B45">
         <v>3</v>
@@ -14798,32 +14795,35 @@
         <v>579</v>
       </c>
       <c r="D45" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>562</v>
+        <v>579</v>
       </c>
       <c r="D46" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>616</v>
+        <v>587</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="C47" t="s">
+        <v>562</v>
       </c>
       <c r="D47" t="s">
-        <v>617</v>
+        <v>588</v>
       </c>
       <c r="E47" t="s">
         <v>617</v>
@@ -14831,32 +14831,29 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>589</v>
+        <v>616</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
       <c r="D48" t="s">
-        <v>590</v>
+        <v>617</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B49">
-        <v>1</v>
-      </c>
-      <c r="C49" t="s">
-        <v>589</v>
+        <v>0</v>
       </c>
       <c r="D49" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -14865,17 +14862,31 @@
         <v>589</v>
       </c>
       <c r="D50" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>595</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s">
+        <v>589</v>
+      </c>
+      <c r="D51" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>500</v>
       </c>
-      <c r="B51">
-        <v>0</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="D52" t="s">
         <v>510</v>
       </c>
     </row>
@@ -14886,7 +14897,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -14930,34 +14941,23 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>624</v>
+        <v>500</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>500</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="D6" t="s">
         <v>510</v>
       </c>
     </row>

--- a/data/dimensions/dimensions.xlsx
+++ b/data/dimensions/dimensions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GIT\data_model_tmp\data\dimensions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GIT\cross_back\initial_data\classifications\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0B6235-AAAC-4EC3-A278-E3028FAB5FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303C2C7F-FCCE-457C-8507-2B20BC5AA717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1080" windowWidth="30900" windowHeight="14460" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="1080" windowWidth="30900" windowHeight="14460" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="21" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2221" uniqueCount="1339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2218" uniqueCount="1338">
   <si>
     <t>id</t>
   </si>
@@ -1912,6 +1912,9 @@
     <t>residential</t>
   </si>
   <si>
+    <t>Residential</t>
+  </si>
+  <si>
     <t>transport</t>
   </si>
   <si>
@@ -4052,12 +4055,6 @@
   </si>
   <si>
     <t>https://www.bfe.admin.ch/ogd62</t>
-  </si>
-  <si>
-    <t>asd</t>
-  </si>
-  <si>
-    <t>other2</t>
   </si>
 </sst>
 </file>
@@ -4478,176 +4475,176 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
   </sheetData>
@@ -4696,12 +4693,12 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -4710,15 +4707,15 @@
         <v>618</v>
       </c>
       <c r="D3" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E3" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -4727,12 +4724,12 @@
         <v>618</v>
       </c>
       <c r="D4" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -4741,12 +4738,12 @@
         <v>618</v>
       </c>
       <c r="D5" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -4755,12 +4752,12 @@
         <v>618</v>
       </c>
       <c r="D6" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -4769,12 +4766,12 @@
         <v>618</v>
       </c>
       <c r="D7" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -4783,12 +4780,12 @@
         <v>618</v>
       </c>
       <c r="D8" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -4797,7 +4794,7 @@
         <v>618</v>
       </c>
       <c r="D9" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -4808,7 +4805,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -4819,12 +4816,12 @@
         <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -4833,12 +4830,12 @@
         <v>622</v>
       </c>
       <c r="D12" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -4847,12 +4844,12 @@
         <v>622</v>
       </c>
       <c r="D13" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -4861,7 +4858,7 @@
         <v>622</v>
       </c>
       <c r="D14" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -4904,245 +4901,245 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D5" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D6" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D7" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D8" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D9" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D10" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D11" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D12" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D13" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D14" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D15" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D16" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D17" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D18" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D19" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -5185,66 +5182,66 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D4" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D5" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D6" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -5291,77 +5288,77 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D4" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D5" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D6" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -5377,7 +5374,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -5400,12 +5397,12 @@
         <v>523</v>
       </c>
       <c r="D10" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -5414,12 +5411,12 @@
         <v>554</v>
       </c>
       <c r="D11" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -5428,7 +5425,7 @@
         <v>554</v>
       </c>
       <c r="D12" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -5529,7 +5526,7 @@
         <v>562</v>
       </c>
       <c r="D19" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -5543,7 +5540,7 @@
         <v>567</v>
       </c>
       <c r="D20" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -5557,7 +5554,7 @@
         <v>567</v>
       </c>
       <c r="D21" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -5571,7 +5568,7 @@
         <v>567</v>
       </c>
       <c r="D22" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -5585,7 +5582,7 @@
         <v>567</v>
       </c>
       <c r="D23" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -5618,710 +5615,710 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
       <c r="D26" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D27" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D28" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D29" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
       <c r="D30" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D31" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B32">
         <v>2</v>
       </c>
       <c r="C32" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D32" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B33">
         <v>3</v>
       </c>
       <c r="C33" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D33" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B34">
         <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D34" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B35">
         <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D35" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B36">
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D36" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B37">
         <v>3</v>
       </c>
       <c r="C37" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D37" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B38">
         <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D38" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B39">
         <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D39" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B40">
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D40" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B41">
         <v>3</v>
       </c>
       <c r="C41" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D41" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B42">
         <v>3</v>
       </c>
       <c r="C42" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D42" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B43">
         <v>3</v>
       </c>
       <c r="C43" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D43" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B44">
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D44" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D45" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B46">
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D46" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B47">
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D47" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B48">
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D48" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B49">
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D49" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B50">
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D50" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B51">
         <v>3</v>
       </c>
       <c r="C51" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D51" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B52">
         <v>3</v>
       </c>
       <c r="C52" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D52" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B53">
         <v>3</v>
       </c>
       <c r="C53" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D53" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B54">
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D54" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B55">
         <v>3</v>
       </c>
       <c r="C55" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D55" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B56">
         <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D56" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B57">
         <v>3</v>
       </c>
       <c r="C57" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D57" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B58">
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D58" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B59">
         <v>3</v>
       </c>
       <c r="C59" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D59" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B60">
         <v>3</v>
       </c>
       <c r="C60" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D60" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B61">
         <v>3</v>
       </c>
       <c r="C61" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D61" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B62">
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D62" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B63">
         <v>1</v>
       </c>
       <c r="C63" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D63" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B64">
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D64" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B65">
         <v>3</v>
       </c>
       <c r="C65" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D65" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B66">
         <v>3</v>
       </c>
       <c r="C66" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D66" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B67">
         <v>3</v>
       </c>
       <c r="C67" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D67" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B68">
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D68" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B69">
         <v>3</v>
       </c>
       <c r="C69" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D69" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B70">
         <v>3</v>
       </c>
       <c r="C70" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D70" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B71">
         <v>3</v>
       </c>
       <c r="C71" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D71" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B72">
         <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D72" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B73">
         <v>3</v>
       </c>
       <c r="C73" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D73" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B74">
         <v>3</v>
       </c>
       <c r="C74" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D74" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B75">
         <v>3</v>
       </c>
       <c r="C75" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D75" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B76">
         <v>2</v>
       </c>
       <c r="C76" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D76" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -6332,315 +6329,315 @@
         <v>1</v>
       </c>
       <c r="C77" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D77" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B78">
         <v>1</v>
       </c>
       <c r="C78" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D78" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B79">
         <v>2</v>
       </c>
       <c r="C79" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D79" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B80">
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D80" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B81">
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D81" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B82">
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D82" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B83">
         <v>2</v>
       </c>
       <c r="C83" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D83" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B84">
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D84" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B85">
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D85" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B86">
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D86" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B87">
         <v>2</v>
       </c>
       <c r="C87" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D87" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B88">
         <v>1</v>
       </c>
       <c r="C88" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D88" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B89">
         <v>2</v>
       </c>
       <c r="C89" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D89" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B90">
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D90" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B91">
         <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D91" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B92">
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D92" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B93">
         <v>2</v>
       </c>
       <c r="C93" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D93" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B94">
         <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D94" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B95">
         <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D95" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B96">
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D96" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B97">
         <v>2</v>
       </c>
       <c r="C97" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D97" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B98">
         <v>1</v>
       </c>
       <c r="C98" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D98" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B99">
         <v>0</v>
       </c>
       <c r="D99" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
@@ -6683,303 +6680,303 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D3" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D4" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D5" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D6" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D7" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D8" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D9" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D10" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D11" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D12" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D13" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="D14" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D15" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D16" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D17" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D18" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D19" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D20" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D21" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B23">
         <v>0</v>
       </c>
       <c r="D23" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -6990,113 +6987,113 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B25">
         <v>0</v>
       </c>
       <c r="D25" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D26" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D27" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D28" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D29" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
       <c r="D30" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="D31" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="D32" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -7145,12 +7142,12 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -7159,12 +7156,12 @@
         <v>601</v>
       </c>
       <c r="D3" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -7173,12 +7170,12 @@
         <v>601</v>
       </c>
       <c r="D4" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -7187,7 +7184,7 @@
         <v>601</v>
       </c>
       <c r="D5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -7198,12 +7195,12 @@
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -7212,12 +7209,12 @@
         <v>609</v>
       </c>
       <c r="D7" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -7226,12 +7223,12 @@
         <v>609</v>
       </c>
       <c r="D8" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -7240,18 +7237,18 @@
         <v>609</v>
       </c>
       <c r="D9" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -7262,60 +7259,60 @@
         <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D13" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D14" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D15" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -7326,7 +7323,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -7369,99 +7366,99 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D4" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D5" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D6" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -7504,102 +7501,102 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D4" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D5" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D6" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="E9" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -7642,91 +7639,91 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="D5" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="D6" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="D7" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="E8" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -7769,489 +7766,489 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D7" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D8" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D9" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D11" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D12" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D13" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D14" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D18" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D19" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D20" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B21">
         <v>0</v>
       </c>
       <c r="D21" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="D23" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="D24" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="D25" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="D26" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
       <c r="D27" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="D28" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="D29" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="D30" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="D31" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D32" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D33" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D34" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D35" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
         <v>1048</v>
       </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="C37" t="s">
-        <v>1047</v>
-      </c>
       <c r="D37" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="D38" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B39">
         <v>0</v>
       </c>
       <c r="D39" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -8292,148 +8289,148 @@
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="D2" s="7">
         <v>2020</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="D3" s="7">
         <v>2017</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="D4" s="7">
         <v>2024</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="D5" s="7">
         <v>2024</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="D6" s="7">
         <v>2024</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="D7" s="7">
         <v>2025</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
   </sheetData>
@@ -8469,269 +8466,269 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D3" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D4" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D5" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D8" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D9" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D10" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="D13" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D14" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D15" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D16" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="D18" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
       <c r="D19" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="D20" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="D21" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="D22" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -8774,185 +8771,185 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D5" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D6" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D7" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D11" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D12" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D13" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="D14" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -8995,196 +8992,196 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D6" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D7" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D8" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D12" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D13" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D14" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -11976,13 +11973,13 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
@@ -11993,1226 +11990,1226 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>1110</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>1108</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1337</v>
+        <v>1111</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>1118</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>1108</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>1124</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>1108</v>
-      </c>
       <c r="E10" s="2" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>1171</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>1110</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>1170</v>
-      </c>
       <c r="E38" s="2" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>1171</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>1195</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>1170</v>
-      </c>
       <c r="E50" s="2" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D62" s="2" t="s">
         <v>1171</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>1208</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>1170</v>
-      </c>
       <c r="E62" s="2" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
   </sheetData>
@@ -13230,10 +13227,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>3</v>
@@ -13244,223 +13241,223 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>1224</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>1223</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>1228</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>1227</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>1232</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>1231</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>1236</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>1235</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>1240</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>1239</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>1248</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>1247</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>1252</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>1251</v>
-      </c>
       <c r="E9" s="2" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>1256</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>1255</v>
-      </c>
       <c r="E10" s="2" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>1260</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>1259</v>
-      </c>
       <c r="E11" s="2" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>1263</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>1262</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
   </sheetData>
@@ -13552,7 +13549,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -14162,17 +14159,6 @@
         <v>0</v>
       </c>
       <c r="D44" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>1338</v>
-      </c>
-      <c r="B45">
-        <v>0</v>
-      </c>
-      <c r="D45" t="s">
         <v>510</v>
       </c>
     </row>
@@ -14183,7 +14169,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -14688,7 +14674,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B38">
         <v>3</v>
@@ -14697,12 +14683,12 @@
         <v>567</v>
       </c>
       <c r="D38" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B39">
         <v>3</v>
@@ -14711,12 +14697,12 @@
         <v>567</v>
       </c>
       <c r="D39" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B40">
         <v>3</v>
@@ -14725,12 +14711,12 @@
         <v>567</v>
       </c>
       <c r="D40" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B41">
         <v>3</v>
@@ -14739,40 +14725,40 @@
         <v>567</v>
       </c>
       <c r="D41" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="D42" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>581</v>
+      </c>
+      <c r="B43">
+        <v>3</v>
+      </c>
+      <c r="C43" t="s">
         <v>579</v>
       </c>
-      <c r="B43">
-        <v>2</v>
-      </c>
-      <c r="C43" t="s">
-        <v>562</v>
-      </c>
       <c r="D43" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B44">
         <v>3</v>
@@ -14781,12 +14767,12 @@
         <v>579</v>
       </c>
       <c r="D44" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B45">
         <v>3</v>
@@ -14795,35 +14781,32 @@
         <v>579</v>
       </c>
       <c r="D45" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>579</v>
+        <v>562</v>
       </c>
       <c r="D46" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>587</v>
+        <v>616</v>
       </c>
       <c r="B47">
-        <v>2</v>
-      </c>
-      <c r="C47" t="s">
-        <v>562</v>
+        <v>0</v>
       </c>
       <c r="D47" t="s">
-        <v>588</v>
+        <v>617</v>
       </c>
       <c r="E47" t="s">
         <v>617</v>
@@ -14831,29 +14814,32 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>616</v>
+        <v>589</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
       <c r="D48" t="s">
-        <v>617</v>
+        <v>590</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>591</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
         <v>589</v>
       </c>
-      <c r="B49">
-        <v>0</v>
-      </c>
       <c r="D49" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -14862,31 +14848,17 @@
         <v>589</v>
       </c>
       <c r="D50" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>595</v>
+        <v>500</v>
       </c>
       <c r="B51">
-        <v>1</v>
-      </c>
-      <c r="C51" t="s">
-        <v>589</v>
+        <v>0</v>
       </c>
       <c r="D51" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>500</v>
-      </c>
-      <c r="B52">
-        <v>0</v>
-      </c>
-      <c r="D52" t="s">
         <v>510</v>
       </c>
     </row>
@@ -14897,7 +14869,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -14941,23 +14913,34 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>622</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
         <v>623</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="D4" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>624</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>500</v>
       </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
         <v>510</v>
       </c>
     </row>

--- a/data/dimensions/dimensions.xlsx
+++ b/data/dimensions/dimensions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adrianamarcucci/Documents/GitHub/cross/data_model_tmp/data/dimensions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GIT\data_model_tmp\data\dimensions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{441F3BF2-49B6-CA41-993B-96FF18D01EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11251CC-EAA3-476A-9BE4-90CB1B5E7584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35820" yWindow="1540" windowWidth="30240" windowHeight="18560" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20544" yWindow="0" windowWidth="20832" windowHeight="16656" tabRatio="808" firstSheet="16" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="21" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2568" uniqueCount="1504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2569" uniqueCount="1504">
   <si>
     <t>id</t>
   </si>
@@ -4572,7 +4572,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4688,8 +4688,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -4990,15 +4990,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{449AD150-DA1C-45F5-B18A-BE0103AD8B74}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="36.1640625" customWidth="1"/>
-    <col min="2" max="2" width="44.1640625" customWidth="1"/>
-    <col min="3" max="3" width="29.83203125" customWidth="1"/>
-    <col min="4" max="4" width="68.83203125" customWidth="1"/>
+    <col min="1" max="1" width="36.109375" customWidth="1"/>
+    <col min="2" max="2" width="44.109375" customWidth="1"/>
+    <col min="3" max="3" width="29.77734375" customWidth="1"/>
+    <col min="4" max="4" width="68.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>1252</v>
       </c>
@@ -5015,7 +5015,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2" s="5" t="s">
         <v>1257</v>
       </c>
@@ -5028,7 +5028,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3" s="5" t="s">
         <v>1260</v>
       </c>
@@ -5043,7 +5043,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4" s="5" t="s">
         <v>1263</v>
       </c>
@@ -5058,7 +5058,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5" s="5" t="s">
         <v>1265</v>
       </c>
@@ -5073,7 +5073,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6" s="5" t="s">
         <v>1268</v>
       </c>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="E6" s="4"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
         <v>1271</v>
       </c>
@@ -5101,7 +5101,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
         <v>1274</v>
       </c>
@@ -5116,7 +5116,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
         <v>1277</v>
       </c>
@@ -5131,7 +5131,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
         <v>1280</v>
       </c>
@@ -5146,7 +5146,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5">
       <c r="A11" s="4" t="s">
         <v>1283</v>
       </c>
@@ -5159,7 +5159,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
         <v>1285</v>
       </c>
@@ -5191,9 +5191,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5210,7 +5210,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>611</v>
       </c>
@@ -5221,7 +5221,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>620</v>
       </c>
@@ -5238,7 +5238,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>623</v>
       </c>
@@ -5252,7 +5252,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>625</v>
       </c>
@@ -5266,7 +5266,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>627</v>
       </c>
@@ -5280,7 +5280,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>629</v>
       </c>
@@ -5294,7 +5294,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>631</v>
       </c>
@@ -5308,7 +5308,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>633</v>
       </c>
@@ -5322,7 +5322,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>613</v>
       </c>
@@ -5333,7 +5333,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>615</v>
       </c>
@@ -5344,7 +5344,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>637</v>
       </c>
@@ -5358,7 +5358,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>639</v>
       </c>
@@ -5372,7 +5372,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>641</v>
       </c>
@@ -5386,7 +5386,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>500</v>
       </c>
@@ -5405,9 +5405,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5424,7 +5424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>644</v>
       </c>
@@ -5435,7 +5435,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>646</v>
       </c>
@@ -5446,7 +5446,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>648</v>
       </c>
@@ -5460,7 +5460,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>650</v>
       </c>
@@ -5474,7 +5474,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>652</v>
       </c>
@@ -5488,7 +5488,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>654</v>
       </c>
@@ -5502,7 +5502,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>656</v>
       </c>
@@ -5516,7 +5516,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>658</v>
       </c>
@@ -5530,7 +5530,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>660</v>
       </c>
@@ -5544,7 +5544,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>662</v>
       </c>
@@ -5558,7 +5558,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>664</v>
       </c>
@@ -5572,7 +5572,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>666</v>
       </c>
@@ -5586,7 +5586,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>668</v>
       </c>
@@ -5600,7 +5600,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>670</v>
       </c>
@@ -5614,7 +5614,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>672</v>
       </c>
@@ -5628,7 +5628,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>674</v>
       </c>
@@ -5642,7 +5642,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>676</v>
       </c>
@@ -5656,7 +5656,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>500</v>
       </c>
@@ -5675,9 +5675,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5694,7 +5694,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>678</v>
       </c>
@@ -5705,7 +5705,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>680</v>
       </c>
@@ -5716,7 +5716,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>682</v>
       </c>
@@ -5730,7 +5730,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>684</v>
       </c>
@@ -5744,7 +5744,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>686</v>
       </c>
@@ -5758,7 +5758,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>500</v>
       </c>
@@ -5777,15 +5777,15 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:H99"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20.6640625" customWidth="1"/>
-    <col min="3" max="3" width="23.83203125" customWidth="1"/>
+    <col min="3" max="3" width="23.77734375" customWidth="1"/>
     <col min="4" max="4" width="32.33203125" customWidth="1"/>
-    <col min="5" max="5" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5805,7 +5805,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>688</v>
       </c>
@@ -5819,7 +5819,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>690</v>
       </c>
@@ -5833,7 +5833,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>692</v>
       </c>
@@ -5850,7 +5850,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>694</v>
       </c>
@@ -5867,7 +5867,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>696</v>
       </c>
@@ -5884,7 +5884,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="15.6">
       <c r="A7" t="s">
         <v>698</v>
       </c>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H7" s="10"/>
     </row>
-    <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="15.6">
       <c r="A8" t="s">
         <v>523</v>
       </c>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="H8" s="10"/>
     </row>
-    <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="15.6">
       <c r="A9" t="s">
         <v>700</v>
       </c>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="H9" s="10"/>
     </row>
-    <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="15.6">
       <c r="A10" t="s">
         <v>554</v>
       </c>
@@ -5950,7 +5950,7 @@
       </c>
       <c r="H10" s="10"/>
     </row>
-    <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="15.6">
       <c r="A11" t="s">
         <v>702</v>
       </c>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="H11" s="10"/>
     </row>
-    <row r="12" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="15.6">
       <c r="A12" t="s">
         <v>704</v>
       </c>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="H12" s="10"/>
     </row>
-    <row r="13" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="15.6">
       <c r="A13" t="s">
         <v>560</v>
       </c>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="H13" s="10"/>
     </row>
-    <row r="14" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="15.6">
       <c r="A14" t="s">
         <v>578</v>
       </c>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="H14" s="10"/>
     </row>
-    <row r="15" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="15.6">
       <c r="A15" t="s">
         <v>580</v>
       </c>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="H15" s="10"/>
     </row>
-    <row r="16" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="15.6">
       <c r="A16" t="s">
         <v>582</v>
       </c>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="H16" s="10"/>
     </row>
-    <row r="17" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" ht="15.6">
       <c r="A17" t="s">
         <v>584</v>
       </c>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="H17" s="10"/>
     </row>
-    <row r="18" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" ht="15.6">
       <c r="A18" t="s">
         <v>566</v>
       </c>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="H18" s="10"/>
     </row>
-    <row r="19" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" ht="15.6">
       <c r="A19" t="s">
         <v>568</v>
       </c>
@@ -6112,7 +6112,7 @@
       </c>
       <c r="H19" s="10"/>
     </row>
-    <row r="20" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" ht="15.6">
       <c r="A20" t="s">
         <v>570</v>
       </c>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="H20" s="10"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>572</v>
       </c>
@@ -6147,7 +6147,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>574</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>576</v>
       </c>
@@ -6181,7 +6181,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>562</v>
       </c>
@@ -6198,7 +6198,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>711</v>
       </c>
@@ -6212,7 +6212,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>713</v>
       </c>
@@ -6229,7 +6229,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8">
       <c r="A27" t="s">
         <v>715</v>
       </c>
@@ -6246,7 +6246,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8">
       <c r="A28" t="s">
         <v>717</v>
       </c>
@@ -6263,7 +6263,7 @@
         <v>1393</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8">
       <c r="A29" t="s">
         <v>719</v>
       </c>
@@ -6277,7 +6277,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8">
       <c r="A30" t="s">
         <v>721</v>
       </c>
@@ -6294,7 +6294,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8">
       <c r="A31" t="s">
         <v>723</v>
       </c>
@@ -6311,7 +6311,7 @@
         <v>1396</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8">
       <c r="A32" t="s">
         <v>725</v>
       </c>
@@ -6325,7 +6325,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>727</v>
       </c>
@@ -6339,7 +6339,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>729</v>
       </c>
@@ -6353,7 +6353,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>731</v>
       </c>
@@ -6370,7 +6370,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>733</v>
       </c>
@@ -6384,7 +6384,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>735</v>
       </c>
@@ -6398,7 +6398,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>737</v>
       </c>
@@ -6412,7 +6412,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>739</v>
       </c>
@@ -6429,7 +6429,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
         <v>741</v>
       </c>
@@ -6443,7 +6443,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>743</v>
       </c>
@@ -6457,7 +6457,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>745</v>
       </c>
@@ -6471,7 +6471,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>747</v>
       </c>
@@ -6488,7 +6488,7 @@
         <v>1399</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
         <v>749</v>
       </c>
@@ -6505,7 +6505,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
         <v>751</v>
       </c>
@@ -6522,7 +6522,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
         <v>753</v>
       </c>
@@ -6539,7 +6539,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
         <v>755</v>
       </c>
@@ -6556,7 +6556,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
         <v>757</v>
       </c>
@@ -6573,7 +6573,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>759</v>
       </c>
@@ -6590,7 +6590,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>761</v>
       </c>
@@ -6604,7 +6604,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>763</v>
       </c>
@@ -6618,7 +6618,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
         <v>765</v>
       </c>
@@ -6632,7 +6632,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>767</v>
       </c>
@@ -6649,7 +6649,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>769</v>
       </c>
@@ -6663,7 +6663,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>771</v>
       </c>
@@ -6677,7 +6677,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>773</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>775</v>
       </c>
@@ -6708,7 +6708,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>777</v>
       </c>
@@ -6722,7 +6722,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>779</v>
       </c>
@@ -6736,7 +6736,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>781</v>
       </c>
@@ -6750,7 +6750,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>783</v>
       </c>
@@ -6767,7 +6767,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>785</v>
       </c>
@@ -6784,7 +6784,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>787</v>
       </c>
@@ -6801,7 +6801,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>789</v>
       </c>
@@ -6815,7 +6815,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>791</v>
       </c>
@@ -6829,7 +6829,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>793</v>
       </c>
@@ -6843,7 +6843,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>795</v>
       </c>
@@ -6860,7 +6860,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>797</v>
       </c>
@@ -6874,7 +6874,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>799</v>
       </c>
@@ -6888,7 +6888,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
         <v>801</v>
       </c>
@@ -6902,7 +6902,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
         <v>803</v>
       </c>
@@ -6919,7 +6919,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6">
       <c r="A72" t="s">
         <v>805</v>
       </c>
@@ -6933,7 +6933,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
         <v>807</v>
       </c>
@@ -6947,7 +6947,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
         <v>809</v>
       </c>
@@ -6961,7 +6961,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
         <v>811</v>
       </c>
@@ -6978,7 +6978,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
         <v>521</v>
       </c>
@@ -6995,7 +6995,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
         <v>814</v>
       </c>
@@ -7012,7 +7012,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
         <v>816</v>
       </c>
@@ -7029,7 +7029,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
         <v>818</v>
       </c>
@@ -7043,7 +7043,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
         <v>820</v>
       </c>
@@ -7057,7 +7057,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>822</v>
       </c>
@@ -7071,7 +7071,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
         <v>824</v>
       </c>
@@ -7088,7 +7088,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
         <v>826</v>
       </c>
@@ -7102,7 +7102,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
         <v>828</v>
       </c>
@@ -7116,7 +7116,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
         <v>830</v>
       </c>
@@ -7130,7 +7130,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
         <v>832</v>
       </c>
@@ -7147,7 +7147,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
         <v>834</v>
       </c>
@@ -7164,7 +7164,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6">
       <c r="A88" t="s">
         <v>836</v>
       </c>
@@ -7181,7 +7181,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
         <v>838</v>
       </c>
@@ -7195,7 +7195,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
         <v>840</v>
       </c>
@@ -7209,7 +7209,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
         <v>842</v>
       </c>
@@ -7223,7 +7223,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
         <v>844</v>
       </c>
@@ -7240,7 +7240,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
         <v>846</v>
       </c>
@@ -7254,7 +7254,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6">
       <c r="A94" t="s">
         <v>848</v>
       </c>
@@ -7268,7 +7268,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6">
       <c r="A95" t="s">
         <v>850</v>
       </c>
@@ -7282,7 +7282,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6">
       <c r="A96" t="s">
         <v>852</v>
       </c>
@@ -7299,7 +7299,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
         <v>854</v>
       </c>
@@ -7316,7 +7316,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
         <v>856</v>
       </c>
@@ -7330,7 +7330,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
         <v>500</v>
       </c>
@@ -7352,14 +7352,14 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:G42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7379,7 +7379,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="15.6">
       <c r="A2" t="s">
         <v>513</v>
       </c>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="G2" s="11"/>
     </row>
-    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="15.6">
       <c r="A3" t="s">
         <v>858</v>
       </c>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="G3" s="11"/>
     </row>
-    <row r="4" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="15.6">
       <c r="A4" t="s">
         <v>878</v>
       </c>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="G4" s="10"/>
     </row>
-    <row r="5" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" ht="15.6">
       <c r="A5" t="s">
         <v>1330</v>
       </c>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="G5" s="10"/>
     </row>
-    <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="15.6">
       <c r="A6" t="s">
         <v>605</v>
       </c>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="G6" s="10"/>
     </row>
-    <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="15.6">
       <c r="A7" t="s">
         <v>864</v>
       </c>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="G7" s="11"/>
     </row>
-    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="15.6">
       <c r="A8" t="s">
         <v>881</v>
       </c>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="G8" s="11"/>
     </row>
-    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="15.6">
       <c r="A9" t="s">
         <v>1332</v>
       </c>
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G9" s="11"/>
     </row>
-    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" ht="15.6">
       <c r="A10" t="s">
         <v>607</v>
       </c>
@@ -7532,7 +7532,7 @@
       </c>
       <c r="G10" s="11"/>
     </row>
-    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="15.6">
       <c r="A11" t="s">
         <v>866</v>
       </c>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="G11" s="11"/>
     </row>
-    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" ht="15.6">
       <c r="A12" t="s">
         <v>882</v>
       </c>
@@ -7568,7 +7568,7 @@
       </c>
       <c r="G12" s="11"/>
     </row>
-    <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" ht="15.6">
       <c r="A13" t="s">
         <v>1333</v>
       </c>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="G13" s="11"/>
     </row>
-    <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" ht="15.6">
       <c r="A14" t="s">
         <v>603</v>
       </c>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G14" s="11"/>
     </row>
-    <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" ht="15.6">
       <c r="A15" t="s">
         <v>862</v>
       </c>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="G15" s="11"/>
     </row>
-    <row r="16" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" ht="15.6">
       <c r="A16" t="s">
         <v>879</v>
       </c>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="G16" s="11"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>920</v>
       </c>
@@ -7654,7 +7654,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>587</v>
       </c>
@@ -7668,7 +7668,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>868</v>
       </c>
@@ -7685,7 +7685,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>884</v>
       </c>
@@ -7702,7 +7702,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>593</v>
       </c>
@@ -7719,7 +7719,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>540</v>
       </c>
@@ -7733,7 +7733,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>870</v>
       </c>
@@ -7750,7 +7750,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>872</v>
       </c>
@@ -7767,7 +7767,7 @@
         <v>1426</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>874</v>
       </c>
@@ -7784,7 +7784,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>876</v>
       </c>
@@ -7801,7 +7801,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>885</v>
       </c>
@@ -7818,7 +7818,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>550</v>
       </c>
@@ -7835,7 +7835,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>891</v>
       </c>
@@ -7849,7 +7849,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>893</v>
       </c>
@@ -7866,7 +7866,7 @@
         <v>1429</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>895</v>
       </c>
@@ -7883,7 +7883,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>897</v>
       </c>
@@ -7900,7 +7900,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>899</v>
       </c>
@@ -7917,7 +7917,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>901</v>
       </c>
@@ -7931,7 +7931,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>860</v>
       </c>
@@ -7945,7 +7945,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>903</v>
       </c>
@@ -7959,7 +7959,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>886</v>
       </c>
@@ -7973,7 +7973,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>888</v>
       </c>
@@ -7987,7 +7987,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>890</v>
       </c>
@@ -8001,7 +8001,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
         <v>905</v>
       </c>
@@ -8015,7 +8015,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>907</v>
       </c>
@@ -8029,7 +8029,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>500</v>
       </c>
@@ -8051,13 +8051,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8077,7 +8077,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>595</v>
       </c>
@@ -8091,7 +8091,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>909</v>
       </c>
@@ -8108,7 +8108,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>911</v>
       </c>
@@ -8125,7 +8125,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>913</v>
       </c>
@@ -8142,7 +8142,7 @@
         <v>1393</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>603</v>
       </c>
@@ -8156,7 +8156,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>916</v>
       </c>
@@ -8173,7 +8173,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>918</v>
       </c>
@@ -8190,7 +8190,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>920</v>
       </c>
@@ -8207,7 +8207,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>922</v>
       </c>
@@ -8221,7 +8221,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>607</v>
       </c>
@@ -8235,7 +8235,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>719</v>
       </c>
@@ -8249,7 +8249,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>926</v>
       </c>
@@ -8266,7 +8266,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>928</v>
       </c>
@@ -8283,7 +8283,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>854</v>
       </c>
@@ -8300,7 +8300,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>587</v>
       </c>
@@ -8314,7 +8314,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>500</v>
       </c>
@@ -8336,14 +8336,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8360,7 +8360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>931</v>
       </c>
@@ -8374,7 +8374,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>933</v>
       </c>
@@ -8388,7 +8388,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>935</v>
       </c>
@@ -8405,7 +8405,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>937</v>
       </c>
@@ -8422,7 +8422,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>939</v>
       </c>
@@ -8439,7 +8439,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>698</v>
       </c>
@@ -8453,7 +8453,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>942</v>
       </c>
@@ -8467,7 +8467,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>944</v>
       </c>
@@ -8481,7 +8481,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>500</v>
       </c>
@@ -8503,13 +8503,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="4" max="4" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8529,7 +8529,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>946</v>
       </c>
@@ -8543,7 +8543,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>948</v>
       </c>
@@ -8557,7 +8557,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>950</v>
       </c>
@@ -8574,7 +8574,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>952</v>
       </c>
@@ -8591,7 +8591,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>954</v>
       </c>
@@ -8608,7 +8608,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>956</v>
       </c>
@@ -8622,7 +8622,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>958</v>
       </c>
@@ -8636,7 +8636,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>960</v>
       </c>
@@ -8653,7 +8653,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>500</v>
       </c>
@@ -8675,14 +8675,14 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="4" max="4" width="33.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8702,7 +8702,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="15.6">
       <c r="A2" t="s">
         <v>963</v>
       </c>
@@ -8717,7 +8717,7 @@
       </c>
       <c r="I2" s="10"/>
     </row>
-    <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="15.6">
       <c r="A3" t="s">
         <v>965</v>
       </c>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="I3" s="10"/>
     </row>
-    <row r="4" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="15.6">
       <c r="A4" t="s">
         <v>967</v>
       </c>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="I4" s="10"/>
     </row>
-    <row r="5" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="15.6">
       <c r="A5" t="s">
         <v>969</v>
       </c>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="I5" s="10"/>
     </row>
-    <row r="6" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="15.6">
       <c r="A6" t="s">
         <v>971</v>
       </c>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="I6" s="10"/>
     </row>
-    <row r="7" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="15.6">
       <c r="A7" t="s">
         <v>973</v>
       </c>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="I7" s="10"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>975</v>
       </c>
@@ -8818,7 +8818,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>500</v>
       </c>
@@ -8840,13 +8840,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:F39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="51.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8866,7 +8866,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>980</v>
       </c>
@@ -8880,7 +8880,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>680</v>
       </c>
@@ -8894,7 +8894,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>682</v>
       </c>
@@ -8911,7 +8911,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>684</v>
       </c>
@@ -8928,7 +8928,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>686</v>
       </c>
@@ -8945,7 +8945,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>987</v>
       </c>
@@ -8959,7 +8959,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>989</v>
       </c>
@@ -8976,7 +8976,7 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>942</v>
       </c>
@@ -8993,7 +8993,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>975</v>
       </c>
@@ -9010,7 +9010,7 @@
         <v>1459</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>993</v>
       </c>
@@ -9027,7 +9027,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>999</v>
       </c>
@@ -9041,7 +9041,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>648</v>
       </c>
@@ -9058,7 +9058,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>658</v>
       </c>
@@ -9075,7 +9075,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>1003</v>
       </c>
@@ -9092,7 +9092,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>1007</v>
       </c>
@@ -9106,7 +9106,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>1009</v>
       </c>
@@ -9123,7 +9123,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>1011</v>
       </c>
@@ -9140,7 +9140,7 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>1013</v>
       </c>
@@ -9157,7 +9157,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>1015</v>
       </c>
@@ -9174,7 +9174,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>1017</v>
       </c>
@@ -9188,7 +9188,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>678</v>
       </c>
@@ -9205,7 +9205,7 @@
         <v>1468</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>644</v>
       </c>
@@ -9222,7 +9222,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>1020</v>
       </c>
@@ -9239,7 +9239,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>1022</v>
       </c>
@@ -9253,7 +9253,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>1024</v>
       </c>
@@ -9270,7 +9270,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>1026</v>
       </c>
@@ -9287,7 +9287,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>1028</v>
       </c>
@@ -9304,7 +9304,7 @@
         <v>1473</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>1030</v>
       </c>
@@ -9321,7 +9321,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>982</v>
       </c>
@@ -9335,7 +9335,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>1032</v>
       </c>
@@ -9349,7 +9349,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>1033</v>
       </c>
@@ -9366,7 +9366,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>1005</v>
       </c>
@@ -9383,7 +9383,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>1035</v>
       </c>
@@ -9400,7 +9400,7 @@
         <v>1393</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>995</v>
       </c>
@@ -9414,7 +9414,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>1037</v>
       </c>
@@ -9428,7 +9428,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>977</v>
       </c>
@@ -9442,7 +9442,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>886</v>
       </c>
@@ -9456,7 +9456,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>997</v>
       </c>
@@ -9478,21 +9478,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A7A0828-5E43-4E29-B5C5-EA3CD8C78A6A}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.5" style="7" customWidth="1"/>
+    <col min="4" max="4" width="4.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.44140625" style="7" customWidth="1"/>
     <col min="7" max="7" width="27.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="62.1640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="7"/>
+    <col min="8" max="8" width="62.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.77734375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="27.6">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -9521,7 +9521,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="27.6">
       <c r="A2" s="7" t="s">
         <v>1294</v>
       </c>
@@ -9541,7 +9541,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="41.4">
       <c r="A3" s="7" t="s">
         <v>1299</v>
       </c>
@@ -9564,7 +9564,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="41.4">
       <c r="A4" s="7" t="s">
         <v>1305</v>
       </c>
@@ -9581,7 +9581,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="41.4">
       <c r="A5" s="7" t="s">
         <v>1276</v>
       </c>
@@ -9601,7 +9601,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="41.4">
       <c r="A6" s="7" t="s">
         <v>1279</v>
       </c>
@@ -9621,7 +9621,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="41.4">
       <c r="A7" s="7" t="s">
         <v>1315</v>
       </c>
@@ -9653,12 +9653,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="4" max="4" width="34.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9678,7 +9679,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>1039</v>
       </c>
@@ -9692,7 +9693,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>692</v>
       </c>
@@ -9709,7 +9710,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>749</v>
       </c>
@@ -9726,7 +9727,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>1041</v>
       </c>
@@ -9743,7 +9744,7 @@
         <v>1479</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>982</v>
       </c>
@@ -9757,7 +9758,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>680</v>
       </c>
@@ -9771,7 +9772,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>682</v>
       </c>
@@ -9788,7 +9789,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>684</v>
       </c>
@@ -9805,7 +9806,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>686</v>
       </c>
@@ -9822,7 +9823,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>1047</v>
       </c>
@@ -9836,7 +9837,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>999</v>
       </c>
@@ -9850,7 +9851,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>1052</v>
       </c>
@@ -9867,7 +9868,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>1054</v>
       </c>
@@ -9884,7 +9885,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>1003</v>
       </c>
@@ -9901,7 +9902,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>1007</v>
       </c>
@@ -9915,7 +9916,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>1022</v>
       </c>
@@ -9929,7 +9930,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>1032</v>
       </c>
@@ -9943,7 +9944,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>1058</v>
       </c>
@@ -9960,7 +9961,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>1060</v>
       </c>
@@ -9977,7 +9978,7 @@
         <v>1393</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>1035</v>
       </c>
@@ -9994,7 +9995,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>1049</v>
       </c>
@@ -10016,9 +10017,9 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10038,7 +10039,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>1039</v>
       </c>
@@ -10052,7 +10053,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>982</v>
       </c>
@@ -10066,7 +10067,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>680</v>
       </c>
@@ -10080,7 +10081,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>682</v>
       </c>
@@ -10097,7 +10098,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>684</v>
       </c>
@@ -10114,7 +10115,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>686</v>
       </c>
@@ -10131,7 +10132,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>1047</v>
       </c>
@@ -10145,7 +10146,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>999</v>
       </c>
@@ -10159,7 +10160,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>1052</v>
       </c>
@@ -10176,7 +10177,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>1054</v>
       </c>
@@ -10193,7 +10194,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>1003</v>
       </c>
@@ -10210,7 +10211,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>1007</v>
       </c>
@@ -10224,7 +10225,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>1022</v>
       </c>
@@ -10238,7 +10239,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>1032</v>
       </c>
@@ -10252,7 +10253,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>1068</v>
       </c>
@@ -10274,12 +10275,13 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="5" max="5" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.44140625" customWidth="1"/>
+    <col min="5" max="5" width="24.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10299,7 +10301,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>1075</v>
       </c>
@@ -10313,7 +10315,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>1039</v>
       </c>
@@ -10327,7 +10329,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>982</v>
       </c>
@@ -10341,7 +10343,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>680</v>
       </c>
@@ -10355,7 +10357,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>682</v>
       </c>
@@ -10372,7 +10374,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>684</v>
       </c>
@@ -10389,7 +10391,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>686</v>
       </c>
@@ -10406,7 +10408,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>1047</v>
       </c>
@@ -10420,7 +10422,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>999</v>
       </c>
@@ -10434,7 +10436,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>1052</v>
       </c>
@@ -10451,7 +10453,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>1054</v>
       </c>
@@ -10468,7 +10470,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>1003</v>
       </c>
@@ -10485,7 +10487,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>1007</v>
       </c>
@@ -10499,7 +10501,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>1022</v>
       </c>
@@ -10513,7 +10515,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>1032</v>
       </c>
@@ -10527,7 +10529,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>1083</v>
       </c>
@@ -10549,9 +10551,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E250"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10568,7 +10570,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -10579,7 +10581,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -10590,7 +10592,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -10601,7 +10603,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -10612,7 +10614,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -10623,7 +10625,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -10634,7 +10636,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -10645,7 +10647,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -10656,7 +10658,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -10667,7 +10669,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -10678,7 +10680,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -10689,7 +10691,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -10700,7 +10702,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -10711,7 +10713,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -10722,7 +10724,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -10733,7 +10735,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -10744,7 +10746,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -10755,7 +10757,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -10766,7 +10768,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -10777,7 +10779,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -10788,7 +10790,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>45</v>
       </c>
@@ -10799,7 +10801,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -10810,7 +10812,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
         <v>49</v>
       </c>
@@ -10821,7 +10823,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
         <v>51</v>
       </c>
@@ -10832,7 +10834,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
         <v>53</v>
       </c>
@@ -10843,7 +10845,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -10854,7 +10856,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
         <v>57</v>
       </c>
@@ -10865,7 +10867,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
         <v>59</v>
       </c>
@@ -10876,7 +10878,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -10887,7 +10889,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -10898,7 +10900,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -10909,7 +10911,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -10920,7 +10922,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -10931,7 +10933,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -10942,7 +10944,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -10953,7 +10955,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -10964,7 +10966,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -10975,7 +10977,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -10986,7 +10988,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -10997,7 +10999,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -11008,7 +11010,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4">
       <c r="A42" t="s">
         <v>85</v>
       </c>
@@ -11019,7 +11021,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -11030,7 +11032,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4">
       <c r="A44" t="s">
         <v>88</v>
       </c>
@@ -11041,7 +11043,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4">
       <c r="A45" t="s">
         <v>90</v>
       </c>
@@ -11052,7 +11054,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4">
       <c r="A46" t="s">
         <v>92</v>
       </c>
@@ -11063,7 +11065,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4">
       <c r="A47" t="s">
         <v>94</v>
       </c>
@@ -11074,7 +11076,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4">
       <c r="A48" t="s">
         <v>96</v>
       </c>
@@ -11085,7 +11087,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4">
       <c r="A49" t="s">
         <v>98</v>
       </c>
@@ -11096,7 +11098,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4">
       <c r="A50" t="s">
         <v>100</v>
       </c>
@@ -11107,7 +11109,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4">
       <c r="A51" t="s">
         <v>102</v>
       </c>
@@ -11118,7 +11120,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4">
       <c r="A52" t="s">
         <v>104</v>
       </c>
@@ -11129,7 +11131,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4">
       <c r="A53" t="s">
         <v>106</v>
       </c>
@@ -11140,7 +11142,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4">
       <c r="A54" t="s">
         <v>108</v>
       </c>
@@ -11151,7 +11153,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4">
       <c r="A55" t="s">
         <v>110</v>
       </c>
@@ -11162,7 +11164,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4">
       <c r="A56" t="s">
         <v>112</v>
       </c>
@@ -11173,7 +11175,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4">
       <c r="A57" t="s">
         <v>114</v>
       </c>
@@ -11184,7 +11186,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4">
       <c r="A58" t="s">
         <v>116</v>
       </c>
@@ -11195,7 +11197,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4">
       <c r="A59" t="s">
         <v>118</v>
       </c>
@@ -11206,7 +11208,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4">
       <c r="A60" t="s">
         <v>120</v>
       </c>
@@ -11217,7 +11219,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4">
       <c r="A61" t="s">
         <v>122</v>
       </c>
@@ -11228,7 +11230,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4">
       <c r="A62" t="s">
         <v>124</v>
       </c>
@@ -11239,7 +11241,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4">
       <c r="A63" t="s">
         <v>126</v>
       </c>
@@ -11250,7 +11252,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4">
       <c r="A64" t="s">
         <v>128</v>
       </c>
@@ -11261,7 +11263,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4">
       <c r="A65" t="s">
         <v>130</v>
       </c>
@@ -11272,7 +11274,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4">
       <c r="A66" t="s">
         <v>132</v>
       </c>
@@ -11283,7 +11285,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4">
       <c r="A67" t="s">
         <v>134</v>
       </c>
@@ -11294,7 +11296,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4">
       <c r="A68" t="s">
         <v>136</v>
       </c>
@@ -11305,7 +11307,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4">
       <c r="A69" t="s">
         <v>138</v>
       </c>
@@ -11316,7 +11318,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4">
       <c r="A70" t="s">
         <v>140</v>
       </c>
@@ -11327,7 +11329,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4">
       <c r="A71" t="s">
         <v>142</v>
       </c>
@@ -11338,7 +11340,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4">
       <c r="A72" t="s">
         <v>144</v>
       </c>
@@ -11349,7 +11351,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4">
       <c r="A73" t="s">
         <v>146</v>
       </c>
@@ -11360,7 +11362,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4">
       <c r="A74" t="s">
         <v>148</v>
       </c>
@@ -11371,7 +11373,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4">
       <c r="A75" t="s">
         <v>150</v>
       </c>
@@ -11382,7 +11384,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4">
       <c r="A76" t="s">
         <v>152</v>
       </c>
@@ -11393,7 +11395,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4">
       <c r="A77" t="s">
         <v>154</v>
       </c>
@@ -11404,7 +11406,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4">
       <c r="A78" t="s">
         <v>156</v>
       </c>
@@ -11415,7 +11417,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4">
       <c r="A79" t="s">
         <v>158</v>
       </c>
@@ -11426,7 +11428,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4">
       <c r="A80" t="s">
         <v>160</v>
       </c>
@@ -11437,7 +11439,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4">
       <c r="A81" t="s">
         <v>162</v>
       </c>
@@ -11448,7 +11450,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4">
       <c r="A82" t="s">
         <v>164</v>
       </c>
@@ -11459,7 +11461,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4">
       <c r="A83" t="s">
         <v>166</v>
       </c>
@@ -11470,7 +11472,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4">
       <c r="A84" t="s">
         <v>168</v>
       </c>
@@ -11481,7 +11483,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4">
       <c r="A85" t="s">
         <v>170</v>
       </c>
@@ -11492,7 +11494,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4">
       <c r="A86" t="s">
         <v>172</v>
       </c>
@@ -11503,7 +11505,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4">
       <c r="A87" t="s">
         <v>174</v>
       </c>
@@ -11514,7 +11516,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4">
       <c r="A88" t="s">
         <v>176</v>
       </c>
@@ -11525,7 +11527,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4">
       <c r="A89" t="s">
         <v>178</v>
       </c>
@@ -11536,7 +11538,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4">
       <c r="A90" t="s">
         <v>180</v>
       </c>
@@ -11547,7 +11549,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4">
       <c r="A91" t="s">
         <v>182</v>
       </c>
@@ -11558,7 +11560,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4">
       <c r="A92" t="s">
         <v>184</v>
       </c>
@@ -11569,7 +11571,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4">
       <c r="A93" t="s">
         <v>186</v>
       </c>
@@ -11580,7 +11582,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4">
       <c r="A94" t="s">
         <v>188</v>
       </c>
@@ -11591,7 +11593,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4">
       <c r="A95" t="s">
         <v>190</v>
       </c>
@@ -11602,7 +11604,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4">
       <c r="A96" t="s">
         <v>192</v>
       </c>
@@ -11613,7 +11615,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4">
       <c r="A97" t="s">
         <v>194</v>
       </c>
@@ -11624,7 +11626,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4">
       <c r="A98" t="s">
         <v>196</v>
       </c>
@@ -11635,7 +11637,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4">
       <c r="A99" t="s">
         <v>198</v>
       </c>
@@ -11646,7 +11648,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4">
       <c r="A100" t="s">
         <v>200</v>
       </c>
@@ -11657,7 +11659,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4">
       <c r="A101" t="s">
         <v>202</v>
       </c>
@@ -11668,7 +11670,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4">
       <c r="A102" t="s">
         <v>204</v>
       </c>
@@ -11679,7 +11681,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4">
       <c r="A103" t="s">
         <v>206</v>
       </c>
@@ -11690,7 +11692,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4">
       <c r="A104" t="s">
         <v>208</v>
       </c>
@@ -11701,7 +11703,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4">
       <c r="A105" t="s">
         <v>210</v>
       </c>
@@ -11712,7 +11714,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4">
       <c r="A106" t="s">
         <v>212</v>
       </c>
@@ -11723,7 +11725,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4">
       <c r="A107" t="s">
         <v>214</v>
       </c>
@@ -11734,7 +11736,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4">
       <c r="A108" t="s">
         <v>216</v>
       </c>
@@ -11745,7 +11747,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4">
       <c r="A109" t="s">
         <v>218</v>
       </c>
@@ -11756,7 +11758,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4">
       <c r="A110" t="s">
         <v>220</v>
       </c>
@@ -11767,7 +11769,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4">
       <c r="A111" t="s">
         <v>222</v>
       </c>
@@ -11778,7 +11780,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4">
       <c r="A112" t="s">
         <v>224</v>
       </c>
@@ -11789,7 +11791,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:4">
       <c r="A113" t="s">
         <v>226</v>
       </c>
@@ -11800,7 +11802,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4">
       <c r="A114" t="s">
         <v>228</v>
       </c>
@@ -11811,7 +11813,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:4">
       <c r="A115" t="s">
         <v>230</v>
       </c>
@@ -11822,7 +11824,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:4">
       <c r="A116" t="s">
         <v>232</v>
       </c>
@@ -11833,7 +11835,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:4">
       <c r="A117" t="s">
         <v>234</v>
       </c>
@@ -11844,7 +11846,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:4">
       <c r="A118" t="s">
         <v>236</v>
       </c>
@@ -11855,7 +11857,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4">
       <c r="A119" t="s">
         <v>238</v>
       </c>
@@ -11866,7 +11868,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:4">
       <c r="A120" t="s">
         <v>240</v>
       </c>
@@ -11877,7 +11879,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4">
       <c r="A121" t="s">
         <v>242</v>
       </c>
@@ -11888,7 +11890,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:4">
       <c r="A122" t="s">
         <v>244</v>
       </c>
@@ -11899,7 +11901,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:4">
       <c r="A123" t="s">
         <v>246</v>
       </c>
@@ -11910,7 +11912,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:4">
       <c r="A124" t="s">
         <v>248</v>
       </c>
@@ -11921,7 +11923,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4">
       <c r="A125" t="s">
         <v>250</v>
       </c>
@@ -11932,7 +11934,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4">
       <c r="A126" t="s">
         <v>252</v>
       </c>
@@ -11943,7 +11945,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:4">
       <c r="A127" t="s">
         <v>254</v>
       </c>
@@ -11954,7 +11956,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:4">
       <c r="A128" t="s">
         <v>256</v>
       </c>
@@ -11965,7 +11967,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4">
       <c r="A129" t="s">
         <v>258</v>
       </c>
@@ -11976,7 +11978,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:4">
       <c r="A130" t="s">
         <v>260</v>
       </c>
@@ -11987,7 +11989,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:4">
       <c r="A131" t="s">
         <v>262</v>
       </c>
@@ -11998,7 +12000,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:4">
       <c r="A132" t="s">
         <v>264</v>
       </c>
@@ -12009,7 +12011,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:4">
       <c r="A133" t="s">
         <v>266</v>
       </c>
@@ -12020,7 +12022,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:4">
       <c r="A134" t="s">
         <v>268</v>
       </c>
@@ -12031,7 +12033,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:4">
       <c r="A135" t="s">
         <v>270</v>
       </c>
@@ -12042,7 +12044,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:4">
       <c r="A136" t="s">
         <v>272</v>
       </c>
@@ -12053,7 +12055,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:4">
       <c r="A137" t="s">
         <v>274</v>
       </c>
@@ -12064,7 +12066,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:4">
       <c r="A138" t="s">
         <v>276</v>
       </c>
@@ -12075,7 +12077,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:4">
       <c r="A139" t="s">
         <v>278</v>
       </c>
@@ -12086,7 +12088,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:4">
       <c r="A140" t="s">
         <v>280</v>
       </c>
@@ -12097,7 +12099,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:4">
       <c r="A141" t="s">
         <v>282</v>
       </c>
@@ -12108,7 +12110,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:4">
       <c r="A142" t="s">
         <v>284</v>
       </c>
@@ -12119,7 +12121,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:4">
       <c r="A143" t="s">
         <v>286</v>
       </c>
@@ -12130,7 +12132,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:4">
       <c r="A144" t="s">
         <v>288</v>
       </c>
@@ -12141,7 +12143,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:4">
       <c r="A145" t="s">
         <v>290</v>
       </c>
@@ -12152,7 +12154,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:4">
       <c r="A146" t="s">
         <v>292</v>
       </c>
@@ -12163,7 +12165,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:4">
       <c r="A147" t="s">
         <v>294</v>
       </c>
@@ -12174,7 +12176,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:4">
       <c r="A148" t="s">
         <v>296</v>
       </c>
@@ -12185,7 +12187,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:4">
       <c r="A149" t="s">
         <v>298</v>
       </c>
@@ -12196,7 +12198,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:4">
       <c r="A150" t="s">
         <v>300</v>
       </c>
@@ -12207,7 +12209,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:4">
       <c r="A151" t="s">
         <v>302</v>
       </c>
@@ -12218,7 +12220,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:4">
       <c r="A152" t="s">
         <v>304</v>
       </c>
@@ -12229,7 +12231,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:4">
       <c r="A153" t="s">
         <v>306</v>
       </c>
@@ -12240,7 +12242,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:4">
       <c r="A154" t="s">
         <v>308</v>
       </c>
@@ -12251,7 +12253,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:4">
       <c r="A155" t="s">
         <v>310</v>
       </c>
@@ -12262,7 +12264,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:4">
       <c r="A156" t="s">
         <v>312</v>
       </c>
@@ -12273,7 +12275,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:4">
       <c r="A157" t="s">
         <v>314</v>
       </c>
@@ -12284,7 +12286,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:4">
       <c r="A158" t="s">
         <v>316</v>
       </c>
@@ -12295,7 +12297,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:4">
       <c r="A159" t="s">
         <v>318</v>
       </c>
@@ -12306,7 +12308,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:4">
       <c r="A160" t="s">
         <v>320</v>
       </c>
@@ -12317,7 +12319,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:4">
       <c r="A161" t="s">
         <v>322</v>
       </c>
@@ -12328,7 +12330,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:4">
       <c r="A162" t="s">
         <v>324</v>
       </c>
@@ -12339,7 +12341,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:4">
       <c r="A163" t="s">
         <v>326</v>
       </c>
@@ -12350,7 +12352,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:4">
       <c r="A164" t="s">
         <v>328</v>
       </c>
@@ -12361,7 +12363,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:4">
       <c r="A165" t="s">
         <v>330</v>
       </c>
@@ -12372,7 +12374,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:4">
       <c r="A166" t="s">
         <v>332</v>
       </c>
@@ -12383,7 +12385,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:4">
       <c r="A167" t="s">
         <v>334</v>
       </c>
@@ -12394,7 +12396,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:4">
       <c r="A168" t="s">
         <v>336</v>
       </c>
@@ -12405,7 +12407,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:4">
       <c r="A169" t="s">
         <v>338</v>
       </c>
@@ -12416,7 +12418,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:4">
       <c r="A170" t="s">
         <v>340</v>
       </c>
@@ -12427,7 +12429,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:4">
       <c r="A171" t="s">
         <v>342</v>
       </c>
@@ -12438,7 +12440,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:4">
       <c r="A172" t="s">
         <v>344</v>
       </c>
@@ -12449,7 +12451,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:4">
       <c r="A173" t="s">
         <v>346</v>
       </c>
@@ -12460,7 +12462,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:4">
       <c r="A174" t="s">
         <v>348</v>
       </c>
@@ -12471,7 +12473,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:4">
       <c r="A175" t="s">
         <v>350</v>
       </c>
@@ -12482,7 +12484,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:4">
       <c r="A176" t="s">
         <v>352</v>
       </c>
@@ -12493,7 +12495,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:4">
       <c r="A177" t="s">
         <v>354</v>
       </c>
@@ -12504,7 +12506,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:4">
       <c r="A178" t="s">
         <v>356</v>
       </c>
@@ -12515,7 +12517,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:4">
       <c r="A179" t="s">
         <v>358</v>
       </c>
@@ -12526,7 +12528,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:4">
       <c r="A180" t="s">
         <v>360</v>
       </c>
@@ -12537,7 +12539,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:4">
       <c r="A181" t="s">
         <v>362</v>
       </c>
@@ -12548,7 +12550,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:4">
       <c r="A182" t="s">
         <v>364</v>
       </c>
@@ -12559,7 +12561,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:4">
       <c r="A183" t="s">
         <v>366</v>
       </c>
@@ -12570,7 +12572,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:4">
       <c r="A184" t="s">
         <v>368</v>
       </c>
@@ -12581,7 +12583,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:4">
       <c r="A185" t="s">
         <v>370</v>
       </c>
@@ -12592,7 +12594,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:4">
       <c r="A186" t="s">
         <v>372</v>
       </c>
@@ -12603,7 +12605,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:4">
       <c r="A187" t="s">
         <v>374</v>
       </c>
@@ -12614,7 +12616,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:4">
       <c r="A188" t="s">
         <v>376</v>
       </c>
@@ -12625,7 +12627,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:4">
       <c r="A189" t="s">
         <v>378</v>
       </c>
@@ -12636,7 +12638,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:4">
       <c r="A190" t="s">
         <v>380</v>
       </c>
@@ -12647,7 +12649,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:4">
       <c r="A191" t="s">
         <v>382</v>
       </c>
@@ -12658,7 +12660,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:4">
       <c r="A192" t="s">
         <v>384</v>
       </c>
@@ -12669,7 +12671,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:4">
       <c r="A193" t="s">
         <v>386</v>
       </c>
@@ -12680,7 +12682,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:4">
       <c r="A194" t="s">
         <v>388</v>
       </c>
@@ -12691,7 +12693,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:4">
       <c r="A195" t="s">
         <v>390</v>
       </c>
@@ -12702,7 +12704,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:4">
       <c r="A196" t="s">
         <v>392</v>
       </c>
@@ -12713,7 +12715,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:4">
       <c r="A197" t="s">
         <v>394</v>
       </c>
@@ -12724,7 +12726,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:4">
       <c r="A198" t="s">
         <v>396</v>
       </c>
@@ -12735,7 +12737,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:4">
       <c r="A199" t="s">
         <v>398</v>
       </c>
@@ -12746,7 +12748,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:4">
       <c r="A200" t="s">
         <v>400</v>
       </c>
@@ -12757,7 +12759,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:4">
       <c r="A201" t="s">
         <v>402</v>
       </c>
@@ -12768,7 +12770,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:4">
       <c r="A202" t="s">
         <v>404</v>
       </c>
@@ -12779,7 +12781,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:4">
       <c r="A203" t="s">
         <v>406</v>
       </c>
@@ -12790,7 +12792,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:4">
       <c r="A204" t="s">
         <v>408</v>
       </c>
@@ -12801,7 +12803,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:4">
       <c r="A205" t="s">
         <v>410</v>
       </c>
@@ -12812,7 +12814,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:4">
       <c r="A206" t="s">
         <v>412</v>
       </c>
@@ -12823,7 +12825,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:4">
       <c r="A207" t="s">
         <v>414</v>
       </c>
@@ -12834,7 +12836,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:4">
       <c r="A208" t="s">
         <v>416</v>
       </c>
@@ -12845,7 +12847,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:4">
       <c r="A209" t="s">
         <v>418</v>
       </c>
@@ -12856,7 +12858,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:4">
       <c r="A210" t="s">
         <v>420</v>
       </c>
@@ -12867,7 +12869,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:4">
       <c r="A211" t="s">
         <v>422</v>
       </c>
@@ -12878,7 +12880,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:4">
       <c r="A212" t="s">
         <v>424</v>
       </c>
@@ -12889,7 +12891,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:4">
       <c r="A213" t="s">
         <v>426</v>
       </c>
@@ -12900,7 +12902,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:4">
       <c r="A214" t="s">
         <v>428</v>
       </c>
@@ -12911,7 +12913,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:4">
       <c r="A215" t="s">
         <v>430</v>
       </c>
@@ -12922,7 +12924,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:4">
       <c r="A216" t="s">
         <v>432</v>
       </c>
@@ -12933,7 +12935,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:4">
       <c r="A217" t="s">
         <v>434</v>
       </c>
@@ -12944,7 +12946,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:4">
       <c r="A218" t="s">
         <v>436</v>
       </c>
@@ -12955,7 +12957,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:4">
       <c r="A219" t="s">
         <v>438</v>
       </c>
@@ -12966,7 +12968,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:4">
       <c r="A220" t="s">
         <v>440</v>
       </c>
@@ -12977,7 +12979,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:4">
       <c r="A221" t="s">
         <v>442</v>
       </c>
@@ -12988,7 +12990,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:4">
       <c r="A222" t="s">
         <v>444</v>
       </c>
@@ -12999,7 +13001,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:4">
       <c r="A223" t="s">
         <v>446</v>
       </c>
@@ -13010,7 +13012,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:4">
       <c r="A224" t="s">
         <v>448</v>
       </c>
@@ -13021,7 +13023,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:4">
       <c r="A225" t="s">
         <v>450</v>
       </c>
@@ -13032,7 +13034,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:4">
       <c r="A226" t="s">
         <v>452</v>
       </c>
@@ -13043,7 +13045,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:4">
       <c r="A227" t="s">
         <v>454</v>
       </c>
@@ -13054,7 +13056,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:4">
       <c r="A228" t="s">
         <v>456</v>
       </c>
@@ -13065,7 +13067,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:4">
       <c r="A229" t="s">
         <v>458</v>
       </c>
@@ -13076,7 +13078,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:4">
       <c r="A230" t="s">
         <v>460</v>
       </c>
@@ -13087,7 +13089,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:4">
       <c r="A231" t="s">
         <v>462</v>
       </c>
@@ -13098,7 +13100,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:4">
       <c r="A232" t="s">
         <v>464</v>
       </c>
@@ -13109,7 +13111,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:4">
       <c r="A233" t="s">
         <v>466</v>
       </c>
@@ -13120,7 +13122,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:4">
       <c r="A234" t="s">
         <v>468</v>
       </c>
@@ -13131,7 +13133,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:4">
       <c r="A235" t="s">
         <v>470</v>
       </c>
@@ -13142,7 +13144,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:4">
       <c r="A236" t="s">
         <v>472</v>
       </c>
@@ -13153,7 +13155,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:4">
       <c r="A237" t="s">
         <v>474</v>
       </c>
@@ -13164,7 +13166,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:4">
       <c r="A238" t="s">
         <v>476</v>
       </c>
@@ -13175,7 +13177,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:4">
       <c r="A239" t="s">
         <v>478</v>
       </c>
@@ -13186,7 +13188,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:4">
       <c r="A240" t="s">
         <v>480</v>
       </c>
@@ -13197,7 +13199,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:4">
       <c r="A241" t="s">
         <v>482</v>
       </c>
@@ -13208,7 +13210,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:4">
       <c r="A242" t="s">
         <v>484</v>
       </c>
@@ -13219,7 +13221,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:4">
       <c r="A243" t="s">
         <v>486</v>
       </c>
@@ -13230,7 +13232,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:4">
       <c r="A244" t="s">
         <v>488</v>
       </c>
@@ -13241,7 +13243,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:4">
       <c r="A245" t="s">
         <v>490</v>
       </c>
@@ -13252,7 +13254,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:4">
       <c r="A246" t="s">
         <v>492</v>
       </c>
@@ -13263,7 +13265,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:4">
       <c r="A247" t="s">
         <v>494</v>
       </c>
@@ -13274,7 +13276,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:4">
       <c r="A248" t="s">
         <v>496</v>
       </c>
@@ -13285,7 +13287,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:4">
       <c r="A249" t="s">
         <v>498</v>
       </c>
@@ -13296,7 +13298,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:4">
       <c r="A250" t="s">
         <v>500</v>
       </c>
@@ -13315,13 +13317,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DADB5FF-7538-427A-AA86-EA055A5F2993}">
   <dimension ref="A1:E73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>1090</v>
       </c>
@@ -13338,7 +13340,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>1093</v>
       </c>
@@ -13355,7 +13357,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
         <v>1097</v>
       </c>
@@ -13372,7 +13374,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
         <v>1099</v>
       </c>
@@ -13389,7 +13391,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>1101</v>
       </c>
@@ -13406,7 +13408,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
         <v>1093</v>
       </c>
@@ -13423,7 +13425,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
         <v>1097</v>
       </c>
@@ -13440,7 +13442,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
         <v>1099</v>
       </c>
@@ -13457,7 +13459,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
         <v>1107</v>
       </c>
@@ -13474,7 +13476,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
         <v>1093</v>
       </c>
@@ -13491,7 +13493,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
         <v>1097</v>
       </c>
@@ -13508,7 +13510,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
         <v>1099</v>
       </c>
@@ -13525,7 +13527,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
         <v>1107</v>
       </c>
@@ -13542,7 +13544,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
         <v>1114</v>
       </c>
@@ -13559,7 +13561,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
         <v>1118</v>
       </c>
@@ -13576,7 +13578,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
         <v>1121</v>
       </c>
@@ -13593,7 +13595,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5">
       <c r="A17" s="2" t="s">
         <v>1124</v>
       </c>
@@ -13610,7 +13612,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5">
       <c r="A18" s="2" t="s">
         <v>1127</v>
       </c>
@@ -13627,7 +13629,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
         <v>1130</v>
       </c>
@@ -13644,7 +13646,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
         <v>1133</v>
       </c>
@@ -13661,7 +13663,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
         <v>1136</v>
       </c>
@@ -13678,7 +13680,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
         <v>1114</v>
       </c>
@@ -13695,7 +13697,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
         <v>1118</v>
       </c>
@@ -13712,7 +13714,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
         <v>1121</v>
       </c>
@@ -13729,7 +13731,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
         <v>1124</v>
       </c>
@@ -13746,7 +13748,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
         <v>1127</v>
       </c>
@@ -13763,7 +13765,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5">
       <c r="A27" s="2" t="s">
         <v>1130</v>
       </c>
@@ -13780,7 +13782,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5">
       <c r="A28" s="2" t="s">
         <v>1133</v>
       </c>
@@ -13797,7 +13799,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
         <v>1136</v>
       </c>
@@ -13814,7 +13816,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5">
       <c r="A30" s="2" t="s">
         <v>1114</v>
       </c>
@@ -13831,7 +13833,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5">
       <c r="A31" s="2" t="s">
         <v>1118</v>
       </c>
@@ -13848,7 +13850,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5">
       <c r="A32" s="2" t="s">
         <v>1121</v>
       </c>
@@ -13865,7 +13867,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5">
       <c r="A33" s="2" t="s">
         <v>1124</v>
       </c>
@@ -13882,7 +13884,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5">
       <c r="A34" s="2" t="s">
         <v>1127</v>
       </c>
@@ -13899,7 +13901,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5">
       <c r="A35" s="2" t="s">
         <v>1130</v>
       </c>
@@ -13916,7 +13918,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5">
       <c r="A36" s="2" t="s">
         <v>1133</v>
       </c>
@@ -13933,7 +13935,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5">
       <c r="A37" s="2" t="s">
         <v>1136</v>
       </c>
@@ -13950,7 +13952,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5">
       <c r="A38" s="2" t="s">
         <v>1155</v>
       </c>
@@ -13967,7 +13969,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5">
       <c r="A39" s="2" t="s">
         <v>1158</v>
       </c>
@@ -13984,7 +13986,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5">
       <c r="A40" s="2" t="s">
         <v>1160</v>
       </c>
@@ -14001,7 +14003,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5">
       <c r="A41" s="2" t="s">
         <v>1162</v>
       </c>
@@ -14018,7 +14020,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5">
       <c r="A42" s="2" t="s">
         <v>1164</v>
       </c>
@@ -14035,7 +14037,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5">
       <c r="A43" s="2" t="s">
         <v>1166</v>
       </c>
@@ -14052,7 +14054,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5">
       <c r="A44" s="2" t="s">
         <v>1168</v>
       </c>
@@ -14069,7 +14071,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5">
       <c r="A45" s="2" t="s">
         <v>1170</v>
       </c>
@@ -14086,7 +14088,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5">
       <c r="A46" s="2" t="s">
         <v>1172</v>
       </c>
@@ -14103,7 +14105,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5">
       <c r="A47" s="2" t="s">
         <v>1174</v>
       </c>
@@ -14120,7 +14122,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5">
       <c r="A48" s="2" t="s">
         <v>1176</v>
       </c>
@@ -14137,7 +14139,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5">
       <c r="A49" s="2" t="s">
         <v>1178</v>
       </c>
@@ -14154,7 +14156,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5">
       <c r="A50" s="2" t="s">
         <v>1155</v>
       </c>
@@ -14171,7 +14173,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5">
       <c r="A51" s="2" t="s">
         <v>1158</v>
       </c>
@@ -14188,7 +14190,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5">
       <c r="A52" s="2" t="s">
         <v>1160</v>
       </c>
@@ -14205,7 +14207,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5">
       <c r="A53" s="2" t="s">
         <v>1162</v>
       </c>
@@ -14222,7 +14224,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>1164</v>
       </c>
@@ -14239,7 +14241,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5">
       <c r="A55" s="2" t="s">
         <v>1166</v>
       </c>
@@ -14256,7 +14258,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5">
       <c r="A56" s="2" t="s">
         <v>1168</v>
       </c>
@@ -14273,7 +14275,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5">
       <c r="A57" s="2" t="s">
         <v>1170</v>
       </c>
@@ -14290,7 +14292,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5">
       <c r="A58" s="2" t="s">
         <v>1172</v>
       </c>
@@ -14307,7 +14309,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5">
       <c r="A59" s="2" t="s">
         <v>1174</v>
       </c>
@@ -14324,7 +14326,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5">
       <c r="A60" s="2" t="s">
         <v>1176</v>
       </c>
@@ -14341,7 +14343,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5">
       <c r="A61" s="2" t="s">
         <v>1178</v>
       </c>
@@ -14358,7 +14360,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5">
       <c r="A62" s="2" t="s">
         <v>1155</v>
       </c>
@@ -14375,7 +14377,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5">
       <c r="A63" s="2" t="s">
         <v>1158</v>
       </c>
@@ -14392,7 +14394,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5">
       <c r="A64" s="2" t="s">
         <v>1160</v>
       </c>
@@ -14409,7 +14411,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5">
       <c r="A65" s="2" t="s">
         <v>1162</v>
       </c>
@@ -14426,7 +14428,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5">
       <c r="A66" s="2" t="s">
         <v>1164</v>
       </c>
@@ -14443,7 +14445,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5">
       <c r="A67" s="2" t="s">
         <v>1166</v>
       </c>
@@ -14460,7 +14462,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5">
       <c r="A68" s="2" t="s">
         <v>1168</v>
       </c>
@@ -14477,7 +14479,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5">
       <c r="A69" s="2" t="s">
         <v>1170</v>
       </c>
@@ -14494,7 +14496,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5">
       <c r="A70" s="2" t="s">
         <v>1172</v>
       </c>
@@ -14511,7 +14513,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5">
       <c r="A71" s="2" t="s">
         <v>1174</v>
       </c>
@@ -14528,7 +14530,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5">
       <c r="A72" s="2" t="s">
         <v>1176</v>
       </c>
@@ -14545,7 +14547,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5">
       <c r="A73" s="2" t="s">
         <v>1178</v>
       </c>
@@ -14570,9 +14572,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5090486-2A70-48F6-BAE3-F43AFB363148}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -14592,7 +14594,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
         <v>1207</v>
       </c>
@@ -14612,7 +14614,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
         <v>1211</v>
       </c>
@@ -14632,7 +14634,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>1213</v>
       </c>
@@ -14652,7 +14654,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
         <v>1217</v>
       </c>
@@ -14672,7 +14674,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
         <v>1221</v>
       </c>
@@ -14692,7 +14694,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
         <v>1225</v>
       </c>
@@ -14712,7 +14714,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
         <v>1229</v>
       </c>
@@ -14732,7 +14734,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
         <v>1232</v>
       </c>
@@ -14752,7 +14754,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
         <v>1236</v>
       </c>
@@ -14772,7 +14774,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
         <v>1240</v>
       </c>
@@ -14792,7 +14794,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
         <v>1243</v>
       </c>
@@ -14812,7 +14814,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
         <v>1246</v>
       </c>
@@ -14832,7 +14834,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
         <v>1249</v>
       </c>
@@ -14860,9 +14862,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14879,7 +14881,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>502</v>
       </c>
@@ -14890,7 +14892,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>504</v>
       </c>
@@ -14901,7 +14903,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>506</v>
       </c>
@@ -14912,7 +14914,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>508</v>
       </c>
@@ -14923,7 +14925,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>500</v>
       </c>
@@ -14942,14 +14944,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14965,8 +14967,11 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F1" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>511</v>
       </c>
@@ -14980,7 +14985,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>513</v>
       </c>
@@ -14997,7 +15002,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>515</v>
       </c>
@@ -15014,7 +15019,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>599</v>
       </c>
@@ -15031,7 +15036,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>517</v>
       </c>
@@ -15048,7 +15053,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>519</v>
       </c>
@@ -15065,7 +15070,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>521</v>
       </c>
@@ -15079,7 +15084,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>523</v>
       </c>
@@ -15093,7 +15098,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>525</v>
       </c>
@@ -15110,7 +15115,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>527</v>
       </c>
@@ -15127,7 +15132,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>529</v>
       </c>
@@ -15147,7 +15152,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>531</v>
       </c>
@@ -15164,7 +15169,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>534</v>
       </c>
@@ -15181,7 +15186,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>536</v>
       </c>
@@ -15198,7 +15203,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>538</v>
       </c>
@@ -15215,7 +15220,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>540</v>
       </c>
@@ -15232,7 +15237,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>542</v>
       </c>
@@ -15249,7 +15254,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>544</v>
       </c>
@@ -15266,7 +15271,7 @@
         <v>1496</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>546</v>
       </c>
@@ -15283,7 +15288,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>548</v>
       </c>
@@ -15300,7 +15305,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>550</v>
       </c>
@@ -15317,7 +15322,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>552</v>
       </c>
@@ -15334,7 +15339,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>554</v>
       </c>
@@ -15351,7 +15356,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>556</v>
       </c>
@@ -15368,7 +15373,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>558</v>
       </c>
@@ -15385,7 +15390,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>560</v>
       </c>
@@ -15402,7 +15407,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>564</v>
       </c>
@@ -15419,7 +15424,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>566</v>
       </c>
@@ -15436,7 +15441,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>568</v>
       </c>
@@ -15453,7 +15458,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>570</v>
       </c>
@@ -15470,7 +15475,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>572</v>
       </c>
@@ -15487,7 +15492,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>574</v>
       </c>
@@ -15504,7 +15509,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>576</v>
       </c>
@@ -15521,7 +15526,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>578</v>
       </c>
@@ -15538,7 +15543,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>580</v>
       </c>
@@ -15555,7 +15560,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>582</v>
       </c>
@@ -15572,7 +15577,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>584</v>
       </c>
@@ -15589,7 +15594,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>562</v>
       </c>
@@ -15606,7 +15611,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
         <v>587</v>
       </c>
@@ -15620,7 +15625,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>589</v>
       </c>
@@ -15637,7 +15642,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>591</v>
       </c>
@@ -15654,7 +15659,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>593</v>
       </c>
@@ -15671,7 +15676,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
         <v>500</v>
       </c>
@@ -15693,13 +15698,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -15719,7 +15724,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>595</v>
       </c>
@@ -15733,7 +15738,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>597</v>
       </c>
@@ -15747,7 +15752,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>603</v>
       </c>
@@ -15761,7 +15766,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>605</v>
       </c>
@@ -15775,7 +15780,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>607</v>
       </c>
@@ -15789,7 +15794,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>521</v>
       </c>
@@ -15803,7 +15808,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>511</v>
       </c>
@@ -15817,7 +15822,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>513</v>
       </c>
@@ -15834,7 +15839,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>515</v>
       </c>
@@ -15851,7 +15856,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>599</v>
       </c>
@@ -15871,7 +15876,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>517</v>
       </c>
@@ -15888,7 +15893,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>519</v>
       </c>
@@ -15905,7 +15910,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>610</v>
       </c>
@@ -15919,7 +15924,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>523</v>
       </c>
@@ -15933,7 +15938,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>525</v>
       </c>
@@ -15950,7 +15955,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>527</v>
       </c>
@@ -15967,7 +15972,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>529</v>
       </c>
@@ -15984,7 +15989,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>531</v>
       </c>
@@ -16004,7 +16009,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>534</v>
       </c>
@@ -16021,7 +16026,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>536</v>
       </c>
@@ -16038,7 +16043,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>538</v>
       </c>
@@ -16055,7 +16060,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>540</v>
       </c>
@@ -16072,7 +16077,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>542</v>
       </c>
@@ -16089,7 +16094,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>544</v>
       </c>
@@ -16106,7 +16111,7 @@
         <v>1496</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>546</v>
       </c>
@@ -16123,7 +16128,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>548</v>
       </c>
@@ -16140,7 +16145,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>550</v>
       </c>
@@ -16157,7 +16162,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>552</v>
       </c>
@@ -16174,7 +16179,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>554</v>
       </c>
@@ -16191,7 +16196,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>556</v>
       </c>
@@ -16208,7 +16213,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>558</v>
       </c>
@@ -16225,7 +16230,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>560</v>
       </c>
@@ -16242,7 +16247,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>564</v>
       </c>
@@ -16259,7 +16264,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>566</v>
       </c>
@@ -16276,7 +16281,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>568</v>
       </c>
@@ -16293,7 +16298,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>570</v>
       </c>
@@ -16310,7 +16315,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>572</v>
       </c>
@@ -16327,7 +16332,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>574</v>
       </c>
@@ -16344,7 +16349,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
         <v>576</v>
       </c>
@@ -16361,7 +16366,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>578</v>
       </c>
@@ -16378,7 +16383,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>580</v>
       </c>
@@ -16395,7 +16400,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>582</v>
       </c>
@@ -16412,7 +16417,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
         <v>584</v>
       </c>
@@ -16429,7 +16434,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
         <v>562</v>
       </c>
@@ -16446,7 +16451,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
         <v>587</v>
       </c>
@@ -16460,7 +16465,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
         <v>589</v>
       </c>
@@ -16477,7 +16482,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
         <v>591</v>
       </c>
@@ -16494,7 +16499,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>593</v>
       </c>
@@ -16511,7 +16516,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>500</v>
       </c>
@@ -16533,9 +16538,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -16552,7 +16557,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>611</v>
       </c>
@@ -16563,7 +16568,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>613</v>
       </c>
@@ -16574,7 +16579,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>615</v>
       </c>
@@ -16585,7 +16590,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>617</v>
       </c>
@@ -16596,7 +16601,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>500</v>
       </c>

--- a/data/dimensions/dimensions.xlsx
+++ b/data/dimensions/dimensions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GIT\data_model_tmp\data\dimensions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11251CC-EAA3-476A-9BE4-90CB1B5E7584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B391B0-2FB8-4C91-8F4E-D151A69671A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20544" yWindow="0" windowWidth="20832" windowHeight="16656" tabRatio="808" firstSheet="16" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20544" yWindow="0" windowWidth="20832" windowHeight="16656" tabRatio="808" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="21" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2569" uniqueCount="1504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2569" uniqueCount="1500">
   <si>
     <t>id</t>
   </si>
@@ -3047,9 +3047,6 @@
     <t>Grid losses across all grid levels</t>
   </si>
   <si>
-    <t>other_elec</t>
-  </si>
-  <si>
     <t>Other uses of electricity</t>
   </si>
   <si>
@@ -3203,9 +3200,6 @@
     <t>Hydrogen used for fuel synthesis</t>
   </si>
   <si>
-    <t>other_h2</t>
-  </si>
-  <si>
     <t>Other uses of hydrogen</t>
   </si>
   <si>
@@ -3260,9 +3254,6 @@
     <t>Methane used for fuel synthesis</t>
   </si>
   <si>
-    <t>other_methane</t>
-  </si>
-  <si>
     <t>Other uses of methane</t>
   </si>
   <si>
@@ -3303,9 +3294,6 @@
   </si>
   <si>
     <t>Liquid fuels used for fuel synthesis</t>
-  </si>
-  <si>
-    <t>other_liquids</t>
   </si>
   <si>
     <t>Other uses of liquid fuels</t>
@@ -5000,176 +4988,176 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>1252</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1253</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>1255</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>1256</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="5" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="5" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="5" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="5" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="5" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="4" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
     </row>
   </sheetData>
@@ -5766,7 +5754,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
     </row>
   </sheetData>
@@ -5802,7 +5790,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5816,7 +5804,7 @@
         <v>689</v>
       </c>
       <c r="F2" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -5830,7 +5818,7 @@
         <v>691</v>
       </c>
       <c r="F3" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -5847,7 +5835,7 @@
         <v>693</v>
       </c>
       <c r="F4" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -5864,7 +5852,7 @@
         <v>695</v>
       </c>
       <c r="F5" t="s">
-        <v>1376</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -5881,7 +5869,7 @@
         <v>697</v>
       </c>
       <c r="F6" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.6">
@@ -5895,7 +5883,7 @@
         <v>699</v>
       </c>
       <c r="F7" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="H7" s="10"/>
     </row>
@@ -5910,7 +5898,7 @@
         <v>524</v>
       </c>
       <c r="F8" t="s">
-        <v>1378</v>
+        <v>1374</v>
       </c>
       <c r="H8" s="10"/>
     </row>
@@ -5928,7 +5916,7 @@
         <v>565</v>
       </c>
       <c r="F9" t="s">
-        <v>1379</v>
+        <v>1375</v>
       </c>
       <c r="H9" s="10"/>
     </row>
@@ -5946,7 +5934,7 @@
         <v>701</v>
       </c>
       <c r="F10" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
       <c r="H10" s="10"/>
     </row>
@@ -5964,7 +5952,7 @@
         <v>703</v>
       </c>
       <c r="F11" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
       <c r="H11" s="10"/>
     </row>
@@ -5982,7 +5970,7 @@
         <v>705</v>
       </c>
       <c r="F12" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -6000,7 +5988,7 @@
         <v>561</v>
       </c>
       <c r="F13" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="H13" s="10"/>
     </row>
@@ -6018,7 +6006,7 @@
         <v>579</v>
       </c>
       <c r="F14" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="H14" s="10"/>
     </row>
@@ -6036,7 +6024,7 @@
         <v>581</v>
       </c>
       <c r="F15" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -6054,7 +6042,7 @@
         <v>583</v>
       </c>
       <c r="F16" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="H16" s="10"/>
     </row>
@@ -6072,7 +6060,7 @@
         <v>585</v>
       </c>
       <c r="F17" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="H17" s="10"/>
     </row>
@@ -6090,7 +6078,7 @@
         <v>706</v>
       </c>
       <c r="F18" t="s">
-        <v>1358</v>
+        <v>1354</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -6108,7 +6096,7 @@
         <v>707</v>
       </c>
       <c r="F19" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -6126,7 +6114,7 @@
         <v>708</v>
       </c>
       <c r="F20" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -6144,7 +6132,7 @@
         <v>709</v>
       </c>
       <c r="F21" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -6161,7 +6149,7 @@
         <v>710</v>
       </c>
       <c r="F22" t="s">
-        <v>1389</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -6178,7 +6166,7 @@
         <v>577</v>
       </c>
       <c r="F23" t="s">
-        <v>1390</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -6195,7 +6183,7 @@
         <v>586</v>
       </c>
       <c r="F24" t="s">
-        <v>1391</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -6209,7 +6197,7 @@
         <v>712</v>
       </c>
       <c r="F25" t="s">
-        <v>1392</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -6226,7 +6214,7 @@
         <v>714</v>
       </c>
       <c r="F26" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -6243,7 +6231,7 @@
         <v>716</v>
       </c>
       <c r="F27" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -6260,7 +6248,7 @@
         <v>718</v>
       </c>
       <c r="F28" t="s">
-        <v>1393</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -6274,7 +6262,7 @@
         <v>720</v>
       </c>
       <c r="F29" t="s">
-        <v>1394</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -6291,7 +6279,7 @@
         <v>722</v>
       </c>
       <c r="F30" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -6308,7 +6296,7 @@
         <v>724</v>
       </c>
       <c r="F31" t="s">
-        <v>1396</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -6367,7 +6355,7 @@
         <v>732</v>
       </c>
       <c r="F35" t="s">
-        <v>1397</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -6426,7 +6414,7 @@
         <v>740</v>
       </c>
       <c r="F39" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -6485,7 +6473,7 @@
         <v>748</v>
       </c>
       <c r="F43" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -6502,7 +6490,7 @@
         <v>750</v>
       </c>
       <c r="F44" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -6519,7 +6507,7 @@
         <v>752</v>
       </c>
       <c r="F45" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -6536,7 +6524,7 @@
         <v>754</v>
       </c>
       <c r="F46" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -6553,7 +6541,7 @@
         <v>756</v>
       </c>
       <c r="F47" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -6570,7 +6558,7 @@
         <v>758</v>
       </c>
       <c r="F48" t="s">
-        <v>1362</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -6587,7 +6575,7 @@
         <v>760</v>
       </c>
       <c r="F49" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -6646,7 +6634,7 @@
         <v>768</v>
       </c>
       <c r="F53" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -6705,7 +6693,7 @@
         <v>776</v>
       </c>
       <c r="F57" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -6764,7 +6752,7 @@
         <v>784</v>
       </c>
       <c r="F61" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -6781,7 +6769,7 @@
         <v>786</v>
       </c>
       <c r="F62" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -6798,7 +6786,7 @@
         <v>788</v>
       </c>
       <c r="F63" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -6857,7 +6845,7 @@
         <v>796</v>
       </c>
       <c r="F67" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -6916,7 +6904,7 @@
         <v>804</v>
       </c>
       <c r="F71" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -6975,7 +6963,7 @@
         <v>812</v>
       </c>
       <c r="F75" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -6992,7 +6980,7 @@
         <v>813</v>
       </c>
       <c r="F76" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -7009,7 +6997,7 @@
         <v>815</v>
       </c>
       <c r="F77" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -7026,7 +7014,7 @@
         <v>817</v>
       </c>
       <c r="F78" t="s">
-        <v>1413</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -7085,7 +7073,7 @@
         <v>825</v>
       </c>
       <c r="F82" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -7144,7 +7132,7 @@
         <v>833</v>
       </c>
       <c r="F86" t="s">
-        <v>1415</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -7161,7 +7149,7 @@
         <v>835</v>
       </c>
       <c r="F87" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -7178,7 +7166,7 @@
         <v>837</v>
       </c>
       <c r="F88" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -7237,7 +7225,7 @@
         <v>845</v>
       </c>
       <c r="F92" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -7296,7 +7284,7 @@
         <v>853</v>
       </c>
       <c r="F96" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -7313,7 +7301,7 @@
         <v>855</v>
       </c>
       <c r="F97" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -7327,7 +7315,7 @@
         <v>857</v>
       </c>
       <c r="F98" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -7338,10 +7326,10 @@
         <v>0</v>
       </c>
       <c r="D99" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="F99" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
     </row>
   </sheetData>
@@ -7376,7 +7364,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15.6">
@@ -7387,10 +7375,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="F2" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
       <c r="G2" s="11"/>
     </row>
@@ -7408,7 +7396,7 @@
         <v>859</v>
       </c>
       <c r="F3" t="s">
-        <v>1396</v>
+        <v>1392</v>
       </c>
       <c r="G3" s="11"/>
     </row>
@@ -7426,13 +7414,13 @@
         <v>732</v>
       </c>
       <c r="F4" t="s">
-        <v>1397</v>
+        <v>1393</v>
       </c>
       <c r="G4" s="10"/>
     </row>
     <row r="5" spans="1:7" ht="15.6">
       <c r="A5" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -7441,10 +7429,10 @@
         <v>513</v>
       </c>
       <c r="D5" t="s">
-        <v>1331</v>
+        <v>1327</v>
       </c>
       <c r="F5" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="G5" s="10"/>
     </row>
@@ -7456,10 +7444,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="F6" t="s">
-        <v>1362</v>
+        <v>1358</v>
       </c>
       <c r="G6" s="10"/>
     </row>
@@ -7477,7 +7465,7 @@
         <v>865</v>
       </c>
       <c r="F7" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="G7" s="11"/>
     </row>
@@ -7495,13 +7483,13 @@
         <v>768</v>
       </c>
       <c r="F8" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" ht="15.6">
       <c r="A9" t="s">
-        <v>1332</v>
+        <v>1328</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -7510,10 +7498,10 @@
         <v>605</v>
       </c>
       <c r="D9" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
       <c r="F9" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="G9" s="11"/>
     </row>
@@ -7525,10 +7513,10 @@
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
       <c r="F10" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="G10" s="11"/>
     </row>
@@ -7546,7 +7534,7 @@
         <v>867</v>
       </c>
       <c r="F11" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="G11" s="11"/>
     </row>
@@ -7564,13 +7552,13 @@
         <v>883</v>
       </c>
       <c r="F12" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:7" ht="15.6">
       <c r="A13" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -7579,10 +7567,10 @@
         <v>607</v>
       </c>
       <c r="D13" t="s">
-        <v>1336</v>
+        <v>1332</v>
       </c>
       <c r="F13" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="G13" s="11"/>
     </row>
@@ -7594,10 +7582,10 @@
         <v>0</v>
       </c>
       <c r="D14" t="s">
-        <v>1325</v>
+        <v>1321</v>
       </c>
       <c r="F14" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="G14" s="11"/>
     </row>
@@ -7615,7 +7603,7 @@
         <v>863</v>
       </c>
       <c r="F15" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="G15" s="11"/>
     </row>
@@ -7633,7 +7621,7 @@
         <v>880</v>
       </c>
       <c r="F16" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="G16" s="11"/>
     </row>
@@ -7648,10 +7636,10 @@
         <v>603</v>
       </c>
       <c r="D17" t="s">
-        <v>1338</v>
+        <v>1334</v>
       </c>
       <c r="F17" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -7662,10 +7650,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="s">
-        <v>1328</v>
+        <v>1324</v>
       </c>
       <c r="F18" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -7682,7 +7670,7 @@
         <v>869</v>
       </c>
       <c r="F19" t="s">
-        <v>1413</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -7699,7 +7687,7 @@
         <v>825</v>
       </c>
       <c r="F20" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -7713,10 +7701,10 @@
         <v>587</v>
       </c>
       <c r="D21" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="F21" t="s">
-        <v>1415</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -7727,10 +7715,10 @@
         <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="F22" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -7747,7 +7735,7 @@
         <v>871</v>
       </c>
       <c r="F23" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -7764,7 +7752,7 @@
         <v>873</v>
       </c>
       <c r="F24" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -7781,7 +7769,7 @@
         <v>875</v>
       </c>
       <c r="F25" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -7798,7 +7786,7 @@
         <v>877</v>
       </c>
       <c r="F26" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -7815,7 +7803,7 @@
         <v>845</v>
       </c>
       <c r="F27" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -7829,10 +7817,10 @@
         <v>540</v>
       </c>
       <c r="D28" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="F28" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -7846,7 +7834,7 @@
         <v>892</v>
       </c>
       <c r="F29" t="s">
-        <v>1423</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -7863,7 +7851,7 @@
         <v>894</v>
       </c>
       <c r="F30" t="s">
-        <v>1429</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -7880,7 +7868,7 @@
         <v>896</v>
       </c>
       <c r="F31" t="s">
-        <v>1430</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -7897,7 +7885,7 @@
         <v>898</v>
       </c>
       <c r="F32" t="s">
-        <v>1431</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -7914,7 +7902,7 @@
         <v>900</v>
       </c>
       <c r="F33" t="s">
-        <v>1432</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -7928,7 +7916,7 @@
         <v>902</v>
       </c>
       <c r="F34" t="s">
-        <v>1424</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -7942,7 +7930,7 @@
         <v>861</v>
       </c>
       <c r="F35" t="s">
-        <v>1433</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -7956,7 +7944,7 @@
         <v>904</v>
       </c>
       <c r="F36" t="s">
-        <v>1358</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -7970,7 +7958,7 @@
         <v>887</v>
       </c>
       <c r="F37" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -7984,7 +7972,7 @@
         <v>889</v>
       </c>
       <c r="F38" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -7998,7 +7986,7 @@
         <v>565</v>
       </c>
       <c r="F39" t="s">
-        <v>1425</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -8012,7 +8000,7 @@
         <v>906</v>
       </c>
       <c r="F40" t="s">
-        <v>1392</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -8026,7 +8014,7 @@
         <v>908</v>
       </c>
       <c r="F41" t="s">
-        <v>1435</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -8037,10 +8025,10 @@
         <v>0</v>
       </c>
       <c r="D42" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="F42" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
     </row>
   </sheetData>
@@ -8074,7 +8062,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8088,7 +8076,7 @@
         <v>712</v>
       </c>
       <c r="F2" t="s">
-        <v>1392</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -8105,7 +8093,7 @@
         <v>910</v>
       </c>
       <c r="F3" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -8122,7 +8110,7 @@
         <v>912</v>
       </c>
       <c r="F4" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8139,7 +8127,7 @@
         <v>914</v>
       </c>
       <c r="F5" t="s">
-        <v>1393</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8153,7 +8141,7 @@
         <v>915</v>
       </c>
       <c r="F6" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8170,7 +8158,7 @@
         <v>917</v>
       </c>
       <c r="F7" t="s">
-        <v>1436</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8187,7 +8175,7 @@
         <v>919</v>
       </c>
       <c r="F8" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8204,7 +8192,7 @@
         <v>921</v>
       </c>
       <c r="F9" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -8218,7 +8206,7 @@
         <v>923</v>
       </c>
       <c r="F10" t="s">
-        <v>1362</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -8232,7 +8220,7 @@
         <v>924</v>
       </c>
       <c r="F11" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -8246,7 +8234,7 @@
         <v>925</v>
       </c>
       <c r="F12" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -8263,7 +8251,7 @@
         <v>927</v>
       </c>
       <c r="F13" t="s">
-        <v>1439</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -8280,7 +8268,7 @@
         <v>929</v>
       </c>
       <c r="F14" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -8297,7 +8285,7 @@
         <v>855</v>
       </c>
       <c r="F15" t="s">
-        <v>1441</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -8311,7 +8299,7 @@
         <v>930</v>
       </c>
       <c r="F16" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -8322,10 +8310,10 @@
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="F17" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
     </row>
   </sheetData>
@@ -8371,7 +8359,7 @@
         <v>932</v>
       </c>
       <c r="E2" t="s">
-        <v>1358</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -8385,7 +8373,7 @@
         <v>934</v>
       </c>
       <c r="E3" t="s">
-        <v>1442</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -8402,7 +8390,7 @@
         <v>936</v>
       </c>
       <c r="E4" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -8419,7 +8407,7 @@
         <v>938</v>
       </c>
       <c r="E5" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -8436,7 +8424,7 @@
         <v>940</v>
       </c>
       <c r="E6" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -8450,7 +8438,7 @@
         <v>941</v>
       </c>
       <c r="E7" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -8464,7 +8452,7 @@
         <v>943</v>
       </c>
       <c r="E8" t="s">
-        <v>1372</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -8478,7 +8466,7 @@
         <v>945</v>
       </c>
       <c r="E9" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -8489,10 +8477,10 @@
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="E10" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
     </row>
   </sheetData>
@@ -8526,7 +8514,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8540,7 +8528,7 @@
         <v>947</v>
       </c>
       <c r="F2" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -8554,7 +8542,7 @@
         <v>949</v>
       </c>
       <c r="F3" t="s">
-        <v>1442</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -8571,7 +8559,7 @@
         <v>951</v>
       </c>
       <c r="F4" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8588,7 +8576,7 @@
         <v>953</v>
       </c>
       <c r="F5" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8605,7 +8593,7 @@
         <v>955</v>
       </c>
       <c r="F6" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8619,7 +8607,7 @@
         <v>957</v>
       </c>
       <c r="F7" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8633,7 +8621,7 @@
         <v>959</v>
       </c>
       <c r="F8" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8650,7 +8638,7 @@
         <v>962</v>
       </c>
       <c r="F9" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -8661,10 +8649,10 @@
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>1446</v>
+        <v>1442</v>
       </c>
       <c r="F10" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
     </row>
   </sheetData>
@@ -8699,7 +8687,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.6">
@@ -8713,7 +8701,7 @@
         <v>964</v>
       </c>
       <c r="F2" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="I2" s="10"/>
     </row>
@@ -8728,7 +8716,7 @@
         <v>966</v>
       </c>
       <c r="F3" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="I3" s="10"/>
     </row>
@@ -8743,7 +8731,7 @@
         <v>968</v>
       </c>
       <c r="F4" t="s">
-        <v>1372</v>
+        <v>1368</v>
       </c>
       <c r="I4" s="10"/>
     </row>
@@ -8761,7 +8749,7 @@
         <v>970</v>
       </c>
       <c r="F5" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="I5" s="10"/>
     </row>
@@ -8779,7 +8767,7 @@
         <v>972</v>
       </c>
       <c r="F6" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="I6" s="10"/>
     </row>
@@ -8797,7 +8785,7 @@
         <v>974</v>
       </c>
       <c r="F7" t="s">
-        <v>1372</v>
+        <v>1368</v>
       </c>
       <c r="I7" s="10"/>
     </row>
@@ -8815,7 +8803,7 @@
         <v>962</v>
       </c>
       <c r="F8" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -8826,10 +8814,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>1445</v>
+        <v>1441</v>
       </c>
       <c r="F9" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
     </row>
   </sheetData>
@@ -8863,7 +8851,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8877,7 +8865,7 @@
         <v>981</v>
       </c>
       <c r="F2" t="s">
-        <v>1449</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -8891,7 +8879,7 @@
         <v>984</v>
       </c>
       <c r="F3" t="s">
-        <v>1451</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -8908,7 +8896,7 @@
         <v>985</v>
       </c>
       <c r="F4" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8925,7 +8913,7 @@
         <v>986</v>
       </c>
       <c r="F5" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8942,7 +8930,7 @@
         <v>687</v>
       </c>
       <c r="F6" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8956,7 +8944,7 @@
         <v>988</v>
       </c>
       <c r="F7" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8973,7 +8961,7 @@
         <v>990</v>
       </c>
       <c r="F8" t="s">
-        <v>1453</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8990,7 +8978,7 @@
         <v>991</v>
       </c>
       <c r="F9" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -9007,7 +8995,7 @@
         <v>992</v>
       </c>
       <c r="F10" t="s">
-        <v>1459</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -9024,21 +9012,21 @@
         <v>994</v>
       </c>
       <c r="F11" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
+        <v>998</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
         <v>999</v>
       </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1000</v>
-      </c>
       <c r="F12" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -9049,13 +9037,13 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D13" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="F13" t="s">
-        <v>1461</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -9066,126 +9054,126 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D14" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F14" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>998</v>
+      </c>
+      <c r="D15" t="s">
         <v>1003</v>
       </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" t="s">
-        <v>999</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1004</v>
-      </c>
       <c r="F15" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="D16" t="s">
         <v>1007</v>
       </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1008</v>
-      </c>
       <c r="F16" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D17" t="s">
         <v>1009</v>
       </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17" t="s">
-        <v>1007</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1010</v>
-      </c>
       <c r="F17" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D18" t="s">
         <v>1011</v>
       </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18" t="s">
-        <v>1007</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1012</v>
-      </c>
       <c r="F18" t="s">
-        <v>1465</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D19" t="s">
         <v>1013</v>
       </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
-        <v>1007</v>
-      </c>
-      <c r="D19" t="s">
-        <v>1014</v>
-      </c>
       <c r="F19" t="s">
-        <v>1466</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D20" t="s">
         <v>1015</v>
       </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1007</v>
-      </c>
-      <c r="D20" t="s">
-        <v>1016</v>
-      </c>
       <c r="F20" t="s">
-        <v>1467</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="D21" t="s">
         <v>1017</v>
       </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="D21" t="s">
-        <v>1018</v>
-      </c>
       <c r="F21" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -9196,13 +9184,13 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="D22" t="s">
         <v>679</v>
       </c>
       <c r="F22" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -9213,112 +9201,112 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="D23" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="F23" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D24" t="s">
         <v>1020</v>
       </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24" t="s">
-        <v>1017</v>
-      </c>
-      <c r="D24" t="s">
-        <v>1021</v>
-      </c>
       <c r="F24" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="D25" t="s">
         <v>1022</v>
       </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="D25" t="s">
-        <v>1023</v>
-      </c>
       <c r="F25" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D26" t="s">
         <v>1024</v>
       </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26" t="s">
-        <v>1022</v>
-      </c>
-      <c r="D26" t="s">
-        <v>1025</v>
-      </c>
       <c r="F26" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D27" t="s">
         <v>1026</v>
       </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27" t="s">
-        <v>1022</v>
-      </c>
-      <c r="D27" t="s">
-        <v>1027</v>
-      </c>
       <c r="F27" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D28" t="s">
         <v>1028</v>
       </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28" t="s">
-        <v>1022</v>
-      </c>
-      <c r="D28" t="s">
-        <v>1029</v>
-      </c>
       <c r="F28" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D29" t="s">
         <v>1030</v>
       </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-      <c r="C29" t="s">
-        <v>1022</v>
-      </c>
-      <c r="D29" t="s">
-        <v>1031</v>
-      </c>
       <c r="F29" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -9332,12 +9320,12 @@
         <v>983</v>
       </c>
       <c r="F30" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -9346,58 +9334,58 @@
         <v>712</v>
       </c>
       <c r="F31" t="s">
-        <v>1392</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D32" t="s">
         <v>1033</v>
       </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s">
-        <v>1032</v>
-      </c>
-      <c r="D32" t="s">
-        <v>1034</v>
-      </c>
       <c r="F32" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D33" t="s">
         <v>1005</v>
       </c>
-      <c r="B33">
-        <v>1</v>
-      </c>
-      <c r="C33" t="s">
-        <v>1032</v>
-      </c>
-      <c r="D33" t="s">
-        <v>1006</v>
-      </c>
       <c r="F33" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D34" t="s">
         <v>1035</v>
       </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-      <c r="C34" t="s">
-        <v>1032</v>
-      </c>
-      <c r="D34" t="s">
-        <v>1036</v>
-      </c>
       <c r="F34" t="s">
-        <v>1393</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -9411,21 +9399,21 @@
         <v>996</v>
       </c>
       <c r="F35" t="s">
-        <v>1455</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="D36" t="s">
         <v>1037</v>
       </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-      <c r="D36" t="s">
-        <v>1038</v>
-      </c>
       <c r="F36" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -9439,7 +9427,7 @@
         <v>978</v>
       </c>
       <c r="F37" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -9453,21 +9441,21 @@
         <v>979</v>
       </c>
       <c r="F38" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
+        <v>500</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="D39" t="s">
         <v>997</v>
       </c>
-      <c r="B39">
-        <v>0</v>
-      </c>
-      <c r="D39" t="s">
-        <v>998</v>
-      </c>
       <c r="F39" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
     </row>
   </sheetData>
@@ -9497,148 +9485,148 @@
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>1287</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>1288</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>1289</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>1090</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>1290</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>1291</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>1292</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>1293</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="27.6">
       <c r="A2" s="7" t="s">
-        <v>1294</v>
+        <v>1290</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
       <c r="D2" s="7">
         <v>2020</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="41.4">
       <c r="A3" s="7" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>1301</v>
+        <v>1297</v>
       </c>
       <c r="D3" s="7">
         <v>2017</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1304</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="41.4">
       <c r="A4" s="7" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
       <c r="D4" s="7">
         <v>2024</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="41.4">
       <c r="A5" s="7" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
       <c r="D5" s="7">
         <v>2024</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="41.4">
       <c r="A6" s="7" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
       <c r="D6" s="7">
         <v>2024</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>1312</v>
+        <v>1308</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="41.4">
       <c r="A7" s="7" t="s">
-        <v>1315</v>
+        <v>1311</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
       <c r="D7" s="7">
         <v>2025</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>1316</v>
+        <v>1312</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>1317</v>
+        <v>1313</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
     </row>
   </sheetData>
@@ -9676,21 +9664,21 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
         <v>1039</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1040</v>
-      </c>
       <c r="F2" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -9701,13 +9689,13 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="D3" t="s">
         <v>693</v>
       </c>
       <c r="F3" t="s">
-        <v>1477</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -9718,30 +9706,30 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="D4" t="s">
         <v>750</v>
       </c>
       <c r="F4" t="s">
-        <v>1478</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D5" t="s">
         <v>1041</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1039</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1042</v>
-      </c>
       <c r="F5" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -9752,10 +9740,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F6" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -9766,10 +9754,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F7" t="s">
-        <v>1451</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -9783,10 +9771,10 @@
         <v>680</v>
       </c>
       <c r="D8" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F8" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -9800,10 +9788,10 @@
         <v>680</v>
       </c>
       <c r="D9" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F9" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -9820,119 +9808,119 @@
         <v>687</v>
       </c>
       <c r="F10" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
         <v>1047</v>
       </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1048</v>
-      </c>
       <c r="F11" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="F12" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D13" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="F13" t="s">
-        <v>1461</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D14" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="F14" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>998</v>
+      </c>
+      <c r="D15" t="s">
         <v>1003</v>
       </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" t="s">
-        <v>999</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1004</v>
-      </c>
       <c r="F15" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="F16" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F17" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -9941,72 +9929,72 @@
         <v>915</v>
       </c>
       <c r="F18" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="D19" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="F19" t="s">
-        <v>1392</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="D20" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="F20" t="s">
-        <v>1393</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D21" t="s">
         <v>1035</v>
       </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
-        <v>1032</v>
-      </c>
-      <c r="D21" t="s">
-        <v>1036</v>
-      </c>
       <c r="F21" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>1049</v>
+        <v>500</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="F22" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
     </row>
   </sheetData>
@@ -10018,6 +10006,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="21.77734375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
@@ -10036,21 +10027,21 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="F2" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -10061,10 +10052,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="F3" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -10075,10 +10066,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F4" t="s">
-        <v>1451</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -10092,10 +10083,10 @@
         <v>680</v>
       </c>
       <c r="D5" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F5" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -10109,10 +10100,10 @@
         <v>680</v>
       </c>
       <c r="D6" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="F6" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -10129,119 +10120,119 @@
         <v>687</v>
       </c>
       <c r="F7" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="F8" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="F9" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D10" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="F10" t="s">
-        <v>1461</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D11" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="F11" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>998</v>
+      </c>
+      <c r="D12" t="s">
         <v>1003</v>
       </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" t="s">
-        <v>999</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1004</v>
-      </c>
       <c r="F12" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="D13" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="F13" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="D14" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="F14" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -10250,21 +10241,21 @@
         <v>924</v>
       </c>
       <c r="F15" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>1068</v>
+        <v>500</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F16" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
     </row>
   </sheetData>
@@ -10277,6 +10268,7 @@
   <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
+    <col min="1" max="1" width="21.88671875" customWidth="1"/>
     <col min="4" max="4" width="29.44140625" customWidth="1"/>
     <col min="5" max="5" width="24.77734375" customWidth="1"/>
   </cols>
@@ -10298,35 +10290,35 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="F2" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="F3" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -10337,10 +10329,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="F4" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -10351,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="F5" t="s">
-        <v>1451</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -10368,10 +10360,10 @@
         <v>680</v>
       </c>
       <c r="D6" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="F6" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -10385,10 +10377,10 @@
         <v>680</v>
       </c>
       <c r="D7" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="F7" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -10405,119 +10397,119 @@
         <v>687</v>
       </c>
       <c r="F8" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="F9" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="F10" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D11" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="F11" t="s">
-        <v>1461</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D12" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="F12" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>998</v>
+      </c>
+      <c r="D13" t="s">
         <v>1003</v>
       </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
-        <v>999</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1004</v>
-      </c>
       <c r="F13" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="D14" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="F14" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="F15" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -10526,21 +10518,21 @@
         <v>923</v>
       </c>
       <c r="F16" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>1083</v>
+        <v>500</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="F17" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
     </row>
   </sheetData>
@@ -13325,13 +13317,13 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
@@ -13342,1226 +13334,1226 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>1094</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>1095</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>1097</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>1095</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>1099</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1105</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>1099</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>1103</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1110</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1111</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>1109</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>1101</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>1113</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>1115</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>1095</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>1119</v>
-      </c>
       <c r="E15" s="2" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>1115</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>1103</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>1119</v>
-      </c>
       <c r="E23" s="2" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1147</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>1115</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>1109</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>1119</v>
-      </c>
       <c r="E31" s="2" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1153</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1157</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>1156</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>1095</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>1160</v>
-      </c>
       <c r="E40" s="2" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2" t="s">
-        <v>1162</v>
+        <v>1158</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>1162</v>
+        <v>1158</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1163</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1169</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1171</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1173</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>1156</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>1180</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>1160</v>
-      </c>
       <c r="E52" s="2" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2" t="s">
-        <v>1162</v>
+        <v>1158</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C53" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>1180</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>1162</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>1184</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>1176</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>1156</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>1180</v>
-      </c>
       <c r="D60" s="2" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>1156</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>1193</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>1160</v>
-      </c>
       <c r="E64" s="2" t="s">
-        <v>1196</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2" t="s">
-        <v>1162</v>
+        <v>1158</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C65" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>1193</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>1162</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1198</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1199</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>1200</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>1202</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>1203</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>1204</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
     </row>
   </sheetData>
@@ -14579,10 +14571,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1206</v>
+        <v>1202</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>3</v>
@@ -14591,267 +14583,267 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1208</v>
+        <v>1204</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1208</v>
+        <v>1204</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="F3" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>1213</v>
+        <v>1209</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1214</v>
+        <v>1210</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1215</v>
+        <v>1211</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1214</v>
+        <v>1210</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1219</v>
+        <v>1215</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>1221</v>
+        <v>1217</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1222</v>
+        <v>1218</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1222</v>
+        <v>1218</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1354</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
       <c r="F7" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1351</v>
+        <v>1347</v>
       </c>
       <c r="F8" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1234</v>
+        <v>1230</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1235</v>
+        <v>1231</v>
       </c>
       <c r="F9" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="F10" t="s">
-        <v>1344</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1352</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="F13" t="s">
-        <v>1347</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="F14" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
     </row>
   </sheetData>
@@ -14933,7 +14925,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
     </row>
   </sheetData>
@@ -14968,7 +14960,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -14982,7 +14974,7 @@
         <v>512</v>
       </c>
       <c r="F2" t="s">
-        <v>1482</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -14999,7 +14991,7 @@
         <v>514</v>
       </c>
       <c r="F3" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -15016,7 +15008,7 @@
         <v>516</v>
       </c>
       <c r="F4" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -15033,7 +15025,7 @@
         <v>600</v>
       </c>
       <c r="F5" t="s">
-        <v>1484</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -15050,7 +15042,7 @@
         <v>518</v>
       </c>
       <c r="F6" t="s">
-        <v>1485</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -15067,7 +15059,7 @@
         <v>520</v>
       </c>
       <c r="F7" t="s">
-        <v>1486</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -15081,7 +15073,7 @@
         <v>522</v>
       </c>
       <c r="F8" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -15095,7 +15087,7 @@
         <v>524</v>
       </c>
       <c r="F9" t="s">
-        <v>1378</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -15112,7 +15104,7 @@
         <v>526</v>
       </c>
       <c r="F10" t="s">
-        <v>1488</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -15129,7 +15121,7 @@
         <v>528</v>
       </c>
       <c r="F11" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -15149,7 +15141,7 @@
         <v>533</v>
       </c>
       <c r="F12" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -15166,7 +15158,7 @@
         <v>532</v>
       </c>
       <c r="F13" t="s">
-        <v>1491</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -15183,7 +15175,7 @@
         <v>535</v>
       </c>
       <c r="F14" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -15200,7 +15192,7 @@
         <v>537</v>
       </c>
       <c r="F15" t="s">
-        <v>1493</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -15217,7 +15209,7 @@
         <v>539</v>
       </c>
       <c r="F16" t="s">
-        <v>1494</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -15234,7 +15226,7 @@
         <v>541</v>
       </c>
       <c r="F17" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -15251,7 +15243,7 @@
         <v>543</v>
       </c>
       <c r="F18" t="s">
-        <v>1495</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -15268,7 +15260,7 @@
         <v>545</v>
       </c>
       <c r="F19" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -15285,7 +15277,7 @@
         <v>547</v>
       </c>
       <c r="F20" t="s">
-        <v>1503</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -15302,7 +15294,7 @@
         <v>549</v>
       </c>
       <c r="F21" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -15319,7 +15311,7 @@
         <v>551</v>
       </c>
       <c r="F22" t="s">
-        <v>1498</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -15336,7 +15328,7 @@
         <v>553</v>
       </c>
       <c r="F23" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -15353,7 +15345,7 @@
         <v>555</v>
       </c>
       <c r="F24" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -15370,7 +15362,7 @@
         <v>557</v>
       </c>
       <c r="F25" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -15387,7 +15379,7 @@
         <v>559</v>
       </c>
       <c r="F26" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -15404,7 +15396,7 @@
         <v>561</v>
       </c>
       <c r="F27" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -15421,7 +15413,7 @@
         <v>565</v>
       </c>
       <c r="F28" t="s">
-        <v>1379</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -15438,7 +15430,7 @@
         <v>567</v>
       </c>
       <c r="F29" t="s">
-        <v>1358</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -15455,7 +15447,7 @@
         <v>569</v>
       </c>
       <c r="F30" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -15472,7 +15464,7 @@
         <v>571</v>
       </c>
       <c r="F31" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -15489,7 +15481,7 @@
         <v>573</v>
       </c>
       <c r="F32" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -15506,7 +15498,7 @@
         <v>575</v>
       </c>
       <c r="F33" t="s">
-        <v>1389</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -15523,7 +15515,7 @@
         <v>577</v>
       </c>
       <c r="F34" t="s">
-        <v>1390</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -15540,7 +15532,7 @@
         <v>579</v>
       </c>
       <c r="F35" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -15557,7 +15549,7 @@
         <v>581</v>
       </c>
       <c r="F36" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -15574,7 +15566,7 @@
         <v>583</v>
       </c>
       <c r="F37" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -15591,7 +15583,7 @@
         <v>585</v>
       </c>
       <c r="F38" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -15608,7 +15600,7 @@
         <v>563</v>
       </c>
       <c r="F39" t="s">
-        <v>1391</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -15622,7 +15614,7 @@
         <v>588</v>
       </c>
       <c r="F40" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -15639,7 +15631,7 @@
         <v>590</v>
       </c>
       <c r="F41" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -15656,7 +15648,7 @@
         <v>592</v>
       </c>
       <c r="F42" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -15673,7 +15665,7 @@
         <v>594</v>
       </c>
       <c r="F43" t="s">
-        <v>1502</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -15684,10 +15676,10 @@
         <v>0</v>
       </c>
       <c r="D44" t="s">
-        <v>1320</v>
+        <v>1316</v>
       </c>
       <c r="F44" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
     </row>
   </sheetData>
@@ -15721,7 +15713,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -15735,7 +15727,7 @@
         <v>596</v>
       </c>
       <c r="F2" t="s">
-        <v>1392</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -15749,7 +15741,7 @@
         <v>598</v>
       </c>
       <c r="F3" t="s">
-        <v>1481</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -15763,7 +15755,7 @@
         <v>604</v>
       </c>
       <c r="F4" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -15777,7 +15769,7 @@
         <v>606</v>
       </c>
       <c r="F5" t="s">
-        <v>1362</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -15791,7 +15783,7 @@
         <v>608</v>
       </c>
       <c r="F6" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -15805,7 +15797,7 @@
         <v>609</v>
       </c>
       <c r="F7" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -15819,7 +15811,7 @@
         <v>512</v>
       </c>
       <c r="F8" t="s">
-        <v>1482</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -15836,7 +15828,7 @@
         <v>514</v>
       </c>
       <c r="F9" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -15853,7 +15845,7 @@
         <v>516</v>
       </c>
       <c r="F10" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -15873,7 +15865,7 @@
         <v>601</v>
       </c>
       <c r="F11" t="s">
-        <v>1484</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -15890,7 +15882,7 @@
         <v>602</v>
       </c>
       <c r="F12" t="s">
-        <v>1485</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -15907,7 +15899,7 @@
         <v>520</v>
       </c>
       <c r="F13" t="s">
-        <v>1486</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -15918,10 +15910,10 @@
         <v>0</v>
       </c>
       <c r="D14" t="s">
-        <v>1355</v>
+        <v>1351</v>
       </c>
       <c r="F14" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -15935,7 +15927,7 @@
         <v>524</v>
       </c>
       <c r="F15" t="s">
-        <v>1378</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -15952,7 +15944,7 @@
         <v>526</v>
       </c>
       <c r="F16" t="s">
-        <v>1488</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -15969,7 +15961,7 @@
         <v>528</v>
       </c>
       <c r="F17" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -15986,7 +15978,7 @@
         <v>530</v>
       </c>
       <c r="F18" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -16006,7 +15998,7 @@
         <v>533</v>
       </c>
       <c r="F19" t="s">
-        <v>1491</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -16023,7 +16015,7 @@
         <v>535</v>
       </c>
       <c r="F20" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -16040,7 +16032,7 @@
         <v>537</v>
       </c>
       <c r="F21" t="s">
-        <v>1493</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -16057,7 +16049,7 @@
         <v>539</v>
       </c>
       <c r="F22" t="s">
-        <v>1494</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -16074,7 +16066,7 @@
         <v>541</v>
       </c>
       <c r="F23" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -16091,7 +16083,7 @@
         <v>543</v>
       </c>
       <c r="F24" t="s">
-        <v>1495</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -16108,7 +16100,7 @@
         <v>545</v>
       </c>
       <c r="F25" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -16125,7 +16117,7 @@
         <v>547</v>
       </c>
       <c r="F26" t="s">
-        <v>1503</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -16142,7 +16134,7 @@
         <v>549</v>
       </c>
       <c r="F27" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -16159,7 +16151,7 @@
         <v>551</v>
       </c>
       <c r="F28" t="s">
-        <v>1498</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -16176,7 +16168,7 @@
         <v>553</v>
       </c>
       <c r="F29" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -16193,7 +16185,7 @@
         <v>555</v>
       </c>
       <c r="F30" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -16210,7 +16202,7 @@
         <v>557</v>
       </c>
       <c r="F31" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -16227,7 +16219,7 @@
         <v>559</v>
       </c>
       <c r="F32" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -16244,7 +16236,7 @@
         <v>561</v>
       </c>
       <c r="F33" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -16261,7 +16253,7 @@
         <v>565</v>
       </c>
       <c r="F34" t="s">
-        <v>1379</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -16278,7 +16270,7 @@
         <v>567</v>
       </c>
       <c r="F35" t="s">
-        <v>1358</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -16295,7 +16287,7 @@
         <v>569</v>
       </c>
       <c r="F36" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -16312,7 +16304,7 @@
         <v>571</v>
       </c>
       <c r="F37" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -16329,7 +16321,7 @@
         <v>573</v>
       </c>
       <c r="F38" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -16346,7 +16338,7 @@
         <v>575</v>
       </c>
       <c r="F39" t="s">
-        <v>1389</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -16363,7 +16355,7 @@
         <v>577</v>
       </c>
       <c r="F40" t="s">
-        <v>1390</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -16380,7 +16372,7 @@
         <v>579</v>
       </c>
       <c r="F41" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -16397,7 +16389,7 @@
         <v>581</v>
       </c>
       <c r="F42" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -16414,7 +16406,7 @@
         <v>583</v>
       </c>
       <c r="F43" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -16431,7 +16423,7 @@
         <v>585</v>
       </c>
       <c r="F44" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -16448,7 +16440,7 @@
         <v>563</v>
       </c>
       <c r="F45" t="s">
-        <v>1391</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -16462,7 +16454,7 @@
         <v>588</v>
       </c>
       <c r="F46" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -16479,7 +16471,7 @@
         <v>590</v>
       </c>
       <c r="F47" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -16496,7 +16488,7 @@
         <v>592</v>
       </c>
       <c r="F48" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -16513,7 +16505,7 @@
         <v>594</v>
       </c>
       <c r="F49" t="s">
-        <v>1502</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -16524,10 +16516,10 @@
         <v>0</v>
       </c>
       <c r="D50" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="F50" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
     </row>
   </sheetData>

--- a/data/dimensions/dimensions.xlsx
+++ b/data/dimensions/dimensions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adrianamarcucci/Documents/GitHub/cross/data_model_tmp/data/dimensions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05733BA1-1793-F747-A875-FBDF62103C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B23B1C-339B-B74E-8E20-ED11479578E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41560" yWindow="2020" windowWidth="23500" windowHeight="19000" tabRatio="808" firstSheet="15" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="41240" yWindow="2040" windowWidth="23500" windowHeight="19000" tabRatio="808" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="21" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2970" uniqueCount="1650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2970" uniqueCount="1651">
   <si>
     <t>id</t>
   </si>
@@ -5004,6 +5004,9 @@
   </si>
   <si>
     <t>Space heating: Electric heater</t>
+  </si>
+  <si>
+    <t>Calliope</t>
   </si>
 </sst>
 </file>
@@ -5103,7 +5106,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5124,7 +5127,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -15989,7 +15991,7 @@
         <v>1156</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1155</v>
+        <v>1650</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>1157</v>
@@ -16049,7 +16051,7 @@
         <v>1166</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>1167</v>
@@ -16426,7 +16428,7 @@
       <c r="D5" t="s">
         <v>595</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" t="s">
         <v>1625</v>
       </c>
       <c r="F5" t="s">
@@ -17408,7 +17410,7 @@
       <c r="D11" t="s">
         <v>595</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" t="s">
         <v>1625</v>
       </c>
       <c r="F11" t="s">

--- a/data/dimensions/dimensions.xlsx
+++ b/data/dimensions/dimensions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adrianamarcucci/Documents/GitHub/cross/data_model_tmp/data/dimensions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jan/git/data_model_tmp/data/dimensions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B23B1C-339B-B74E-8E20-ED11479578E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2421DD3-7B23-2649-BD12-8E549041BD07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41240" yWindow="2040" windowWidth="23500" windowHeight="19000" tabRatio="808" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="620" windowWidth="27520" windowHeight="22440" tabRatio="808" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="21" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2970" uniqueCount="1651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3010" uniqueCount="1677">
   <si>
     <t>id</t>
   </si>
@@ -5007,6 +5007,84 @@
   </si>
   <si>
     <t>Calliope</t>
+  </si>
+  <si>
+    <t>evflex</t>
+  </si>
+  <si>
+    <t>pathfndr-sr5</t>
+  </si>
+  <si>
+    <t>no-exp</t>
+  </si>
+  <si>
+    <t>evflex-no-exp</t>
+  </si>
+  <si>
+    <t>EV flexibility without grid expansion</t>
+  </si>
+  <si>
+    <t>hpflex</t>
+  </si>
+  <si>
+    <t>pathfndr-sr6</t>
+  </si>
+  <si>
+    <t>hpflex-no-exp</t>
+  </si>
+  <si>
+    <t>Heatpump flexibility without grid expansion</t>
+  </si>
+  <si>
+    <t>noflex</t>
+  </si>
+  <si>
+    <t>pathfndr-sr7</t>
+  </si>
+  <si>
+    <t>noflex-no-exp</t>
+  </si>
+  <si>
+    <t>No flexibility without grid expansion</t>
+  </si>
+  <si>
+    <t>bothflex</t>
+  </si>
+  <si>
+    <t>pathfndr-sr8</t>
+  </si>
+  <si>
+    <t>bothflex-no-exp</t>
+  </si>
+  <si>
+    <t>EV and heatpump flexibility without grid expansion</t>
+  </si>
+  <si>
+    <t>exp</t>
+  </si>
+  <si>
+    <t>evflex-exp</t>
+  </si>
+  <si>
+    <t>EV flexibility with grid expansion</t>
+  </si>
+  <si>
+    <t>hpflex-exp</t>
+  </si>
+  <si>
+    <t>Heatpump flexibility with grid expansion</t>
+  </si>
+  <si>
+    <t>noflex-exp</t>
+  </si>
+  <si>
+    <t>No flexibility with grid expansion</t>
+  </si>
+  <si>
+    <t>bothflex-exp</t>
+  </si>
+  <si>
+    <t>EV and heatpump flexibility with grid expansion</t>
   </si>
 </sst>
 </file>
@@ -14702,7 +14780,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DADB5FF-7538-427A-AA86-EA055A5F2993}">
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
@@ -15948,6 +16026,142 @@
       </c>
       <c r="E73" s="2" t="s">
         <v>1152</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1652</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1653</v>
+      </c>
+      <c r="D74" t="s">
+        <v>1654</v>
+      </c>
+      <c r="E74" t="s">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1653</v>
+      </c>
+      <c r="D75" t="s">
+        <v>1658</v>
+      </c>
+      <c r="E75" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1661</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1653</v>
+      </c>
+      <c r="D76" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E76" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1665</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1653</v>
+      </c>
+      <c r="D77" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E77" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1652</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D78" t="s">
+        <v>1669</v>
+      </c>
+      <c r="E78" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D79" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E79" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1661</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D80" t="s">
+        <v>1673</v>
+      </c>
+      <c r="E80" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1665</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D81" t="s">
+        <v>1675</v>
+      </c>
+      <c r="E81" t="s">
+        <v>1676</v>
       </c>
     </row>
   </sheetData>
